--- a/GHtoRB2_songids.xlsx
+++ b/GHtoRB2_songids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\RBDLC\reference\!GHtoRB2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C16938-AF3D-4009-A640-209F5292BEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DD2A12-D48E-4E86-B9C3-CBF6185B7A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AE99FE45-D305-4219-A47C-654285C6D506}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="324">
   <si>
     <t>Last Updated: 3/13/26</t>
   </si>
@@ -11089,7 +11089,9 @@
       <c r="D704" s="3">
         <v>4200699</v>
       </c>
-      <c r="E704" s="3"/>
+      <c r="E704" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F704" s="3"/>
       <c r="G704" s="3"/>
     </row>
@@ -11106,7 +11108,9 @@
       <c r="D705" s="3">
         <v>4200700</v>
       </c>
-      <c r="E705" s="3"/>
+      <c r="E705" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F705" s="3"/>
       <c r="G705" s="3"/>
     </row>
@@ -11123,7 +11127,9 @@
       <c r="D706" s="3">
         <v>4200701</v>
       </c>
-      <c r="E706" s="3"/>
+      <c r="E706" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F706" s="3"/>
       <c r="G706" s="3"/>
     </row>
@@ -11140,7 +11146,9 @@
       <c r="D707" s="3">
         <v>4200702</v>
       </c>
-      <c r="E707" s="3"/>
+      <c r="E707" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F707" s="3"/>
       <c r="G707" s="3"/>
     </row>
@@ -11157,7 +11165,9 @@
       <c r="D708" s="3">
         <v>4200703</v>
       </c>
-      <c r="E708" s="3"/>
+      <c r="E708" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F708" s="3"/>
       <c r="G708" s="3"/>
     </row>
@@ -11174,7 +11184,9 @@
       <c r="D709" s="3">
         <v>4200704</v>
       </c>
-      <c r="E709" s="3"/>
+      <c r="E709" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F709" s="3"/>
       <c r="G709" s="3"/>
     </row>
@@ -11191,7 +11203,9 @@
       <c r="D710" s="3">
         <v>4200705</v>
       </c>
-      <c r="E710" s="3"/>
+      <c r="E710" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F710" s="3"/>
       <c r="G710" s="3"/>
     </row>
@@ -11208,7 +11222,9 @@
       <c r="D711" s="3">
         <v>4200706</v>
       </c>
-      <c r="E711" s="3"/>
+      <c r="E711" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F711" s="3"/>
       <c r="G711" s="3"/>
     </row>
@@ -11225,7 +11241,9 @@
       <c r="D712" s="3">
         <v>4200707</v>
       </c>
-      <c r="E712" s="3"/>
+      <c r="E712" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F712" s="3"/>
       <c r="G712" s="3"/>
     </row>
@@ -11242,7 +11260,9 @@
       <c r="D713" s="3">
         <v>4200708</v>
       </c>
-      <c r="E713" s="3"/>
+      <c r="E713" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F713" s="3"/>
       <c r="G713" s="3"/>
     </row>
@@ -11259,7 +11279,9 @@
       <c r="D714" s="3">
         <v>4200709</v>
       </c>
-      <c r="E714" s="3"/>
+      <c r="E714" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F714" s="3"/>
       <c r="G714" s="3"/>
     </row>
@@ -11276,7 +11298,9 @@
       <c r="D715" s="3">
         <v>4200710</v>
       </c>
-      <c r="E715" s="3"/>
+      <c r="E715" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F715" s="3"/>
       <c r="G715" s="3"/>
     </row>
@@ -11293,7 +11317,9 @@
       <c r="D716" s="3">
         <v>4200711</v>
       </c>
-      <c r="E716" s="3"/>
+      <c r="E716" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F716" s="3"/>
       <c r="G716" s="3"/>
     </row>
@@ -11310,7 +11336,9 @@
       <c r="D717" s="3">
         <v>4200712</v>
       </c>
-      <c r="E717" s="3"/>
+      <c r="E717" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F717" s="3"/>
       <c r="G717" s="3"/>
     </row>
@@ -11327,7 +11355,9 @@
       <c r="D718" s="3">
         <v>4200713</v>
       </c>
-      <c r="E718" s="3"/>
+      <c r="E718" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F718" s="3"/>
       <c r="G718" s="3"/>
     </row>
@@ -11344,7 +11374,9 @@
       <c r="D719" s="3">
         <v>4200714</v>
       </c>
-      <c r="E719" s="3"/>
+      <c r="E719" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F719" s="3"/>
       <c r="G719" s="3"/>
     </row>
@@ -11361,7 +11393,9 @@
       <c r="D720" s="3">
         <v>4200715</v>
       </c>
-      <c r="E720" s="3"/>
+      <c r="E720" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F720" s="3"/>
       <c r="G720" s="3"/>
     </row>
@@ -11378,7 +11412,9 @@
       <c r="D721" s="3">
         <v>4200716</v>
       </c>
-      <c r="E721" s="3"/>
+      <c r="E721" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F721" s="3"/>
       <c r="G721" s="3"/>
     </row>
@@ -11395,7 +11431,9 @@
       <c r="D722" s="3">
         <v>4200717</v>
       </c>
-      <c r="E722" s="3"/>
+      <c r="E722" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F722" s="3"/>
       <c r="G722" s="3"/>
     </row>
@@ -11412,7 +11450,9 @@
       <c r="D723" s="3">
         <v>4200718</v>
       </c>
-      <c r="E723" s="3"/>
+      <c r="E723" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F723" s="3"/>
       <c r="G723" s="3"/>
     </row>
@@ -11429,7 +11469,9 @@
       <c r="D724" s="3">
         <v>4200719</v>
       </c>
-      <c r="E724" s="3"/>
+      <c r="E724" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F724" s="3"/>
       <c r="G724" s="3"/>
     </row>
@@ -11446,7 +11488,9 @@
       <c r="D725" s="3">
         <v>4200720</v>
       </c>
-      <c r="E725" s="3"/>
+      <c r="E725" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F725" s="3"/>
       <c r="G725" s="3"/>
     </row>
@@ -11528,7 +11572,9 @@
       <c r="D731" s="3">
         <v>4200726</v>
       </c>
-      <c r="E731" s="3"/>
+      <c r="E731" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F731" s="3"/>
       <c r="G731" s="3"/>
     </row>
@@ -11649,7 +11695,9 @@
       <c r="D740" s="3">
         <v>4200735</v>
       </c>
-      <c r="E740" s="3"/>
+      <c r="E740" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F740" s="3"/>
       <c r="G740" s="3"/>
     </row>
@@ -11783,7 +11831,9 @@
       <c r="D750" s="3">
         <v>4200745</v>
       </c>
-      <c r="E750" s="3"/>
+      <c r="E750" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F750" s="3"/>
       <c r="G750" s="3"/>
     </row>
@@ -11878,7 +11928,9 @@
       <c r="D757" s="3">
         <v>4200752</v>
       </c>
-      <c r="E757" s="3"/>
+      <c r="E757" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F757" s="3"/>
       <c r="G757" s="3"/>
     </row>
@@ -12025,7 +12077,9 @@
       <c r="D768" s="3">
         <v>4200763</v>
       </c>
-      <c r="E768" s="3"/>
+      <c r="E768" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F768" s="3"/>
       <c r="G768" s="3"/>
     </row>
@@ -12042,7 +12096,9 @@
       <c r="D769" s="3">
         <v>4200764</v>
       </c>
-      <c r="E769" s="3"/>
+      <c r="E769" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F769" s="3"/>
       <c r="G769" s="3"/>
     </row>
@@ -12059,7 +12115,9 @@
       <c r="D770" s="3">
         <v>4200765</v>
       </c>
-      <c r="E770" s="3"/>
+      <c r="E770" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F770" s="3"/>
       <c r="G770" s="3"/>
     </row>
@@ -12076,7 +12134,9 @@
       <c r="D771" s="3">
         <v>4200766</v>
       </c>
-      <c r="E771" s="3"/>
+      <c r="E771" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F771" s="3"/>
       <c r="G771" s="3"/>
     </row>
@@ -12093,7 +12153,9 @@
       <c r="D772" s="3">
         <v>4200767</v>
       </c>
-      <c r="E772" s="3"/>
+      <c r="E772" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F772" s="3"/>
       <c r="G772" s="3"/>
     </row>
@@ -12110,7 +12172,9 @@
       <c r="D773" s="3">
         <v>4200768</v>
       </c>
-      <c r="E773" s="3"/>
+      <c r="E773" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F773" s="3"/>
       <c r="G773" s="3"/>
     </row>
@@ -12127,7 +12191,9 @@
       <c r="D774" s="3">
         <v>4200769</v>
       </c>
-      <c r="E774" s="3"/>
+      <c r="E774" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F774" s="3"/>
       <c r="G774" s="3"/>
     </row>
@@ -12144,7 +12210,9 @@
       <c r="D775" s="3">
         <v>4200770</v>
       </c>
-      <c r="E775" s="3"/>
+      <c r="E775" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F775" s="3"/>
       <c r="G775" s="3"/>
     </row>
@@ -12161,7 +12229,9 @@
       <c r="D776" s="3">
         <v>4200771</v>
       </c>
-      <c r="E776" s="3"/>
+      <c r="E776" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F776" s="3"/>
       <c r="G776" s="3"/>
     </row>
@@ -12178,7 +12248,9 @@
       <c r="D777" s="3">
         <v>4200772</v>
       </c>
-      <c r="E777" s="3"/>
+      <c r="E777" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F777" s="3"/>
       <c r="G777" s="3"/>
     </row>
@@ -12195,7 +12267,9 @@
       <c r="D778" s="3">
         <v>4200773</v>
       </c>
-      <c r="E778" s="3"/>
+      <c r="E778" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F778" s="3"/>
       <c r="G778" s="3"/>
     </row>
@@ -12212,7 +12286,9 @@
       <c r="D779" s="3">
         <v>4200774</v>
       </c>
-      <c r="E779" s="3"/>
+      <c r="E779" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F779" s="3"/>
       <c r="G779" s="3"/>
     </row>
@@ -12229,7 +12305,9 @@
       <c r="D780" s="3">
         <v>4200775</v>
       </c>
-      <c r="E780" s="3"/>
+      <c r="E780" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F780" s="3"/>
       <c r="G780" s="3"/>
     </row>
@@ -12246,7 +12324,9 @@
       <c r="D781" s="3">
         <v>4200776</v>
       </c>
-      <c r="E781" s="3"/>
+      <c r="E781" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F781" s="3"/>
       <c r="G781" s="3"/>
     </row>
@@ -12263,7 +12343,9 @@
       <c r="D782" s="3">
         <v>4200777</v>
       </c>
-      <c r="E782" s="3"/>
+      <c r="E782" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F782" s="3"/>
       <c r="G782" s="3"/>
     </row>
@@ -12280,7 +12362,9 @@
       <c r="D783" s="3">
         <v>4200778</v>
       </c>
-      <c r="E783" s="3"/>
+      <c r="E783" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F783" s="3"/>
       <c r="G783" s="3"/>
     </row>
@@ -12297,7 +12381,9 @@
       <c r="D784" s="3">
         <v>4200779</v>
       </c>
-      <c r="E784" s="3"/>
+      <c r="E784" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F784" s="3"/>
       <c r="G784" s="3"/>
     </row>
@@ -12314,7 +12400,9 @@
       <c r="D785" s="3">
         <v>4200780</v>
       </c>
-      <c r="E785" s="3"/>
+      <c r="E785" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F785" s="3"/>
       <c r="G785" s="3"/>
     </row>
@@ -12331,7 +12419,9 @@
       <c r="D786" s="3">
         <v>4200781</v>
       </c>
-      <c r="E786" s="3"/>
+      <c r="E786" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F786" s="3"/>
       <c r="G786" s="3"/>
     </row>
@@ -12348,7 +12438,9 @@
       <c r="D787" s="3">
         <v>4200782</v>
       </c>
-      <c r="E787" s="3"/>
+      <c r="E787" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F787" s="3"/>
       <c r="G787" s="3"/>
     </row>
@@ -12365,7 +12457,9 @@
       <c r="D788" s="3">
         <v>4200783</v>
       </c>
-      <c r="E788" s="3"/>
+      <c r="E788" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F788" s="3"/>
       <c r="G788" s="3"/>
     </row>
@@ -12382,7 +12476,9 @@
       <c r="D789" s="3">
         <v>4200784</v>
       </c>
-      <c r="E789" s="3"/>
+      <c r="E789" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F789" s="3"/>
       <c r="G789" s="3"/>
     </row>
@@ -12399,7 +12495,9 @@
       <c r="D790" s="3">
         <v>4200785</v>
       </c>
-      <c r="E790" s="3"/>
+      <c r="E790" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F790" s="3"/>
       <c r="G790" s="3"/>
     </row>
@@ -12416,7 +12514,9 @@
       <c r="D791" s="3">
         <v>4200786</v>
       </c>
-      <c r="E791" s="3"/>
+      <c r="E791" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F791" s="3"/>
       <c r="G791" s="3"/>
     </row>
@@ -12433,7 +12533,9 @@
       <c r="D792" s="3">
         <v>4200787</v>
       </c>
-      <c r="E792" s="3"/>
+      <c r="E792" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F792" s="3"/>
       <c r="G792" s="3"/>
     </row>
@@ -12450,7 +12552,9 @@
       <c r="D793" s="3">
         <v>4200788</v>
       </c>
-      <c r="E793" s="3"/>
+      <c r="E793" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F793" s="3"/>
       <c r="G793" s="3"/>
     </row>
@@ -12467,7 +12571,9 @@
       <c r="D794" s="3">
         <v>4200789</v>
       </c>
-      <c r="E794" s="3"/>
+      <c r="E794" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F794" s="3"/>
       <c r="G794" s="3"/>
     </row>
@@ -12484,7 +12590,9 @@
       <c r="D795" s="3">
         <v>4200790</v>
       </c>
-      <c r="E795" s="3"/>
+      <c r="E795" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F795" s="3"/>
       <c r="G795" s="3"/>
     </row>
@@ -12501,7 +12609,9 @@
       <c r="D796" s="3">
         <v>4200791</v>
       </c>
-      <c r="E796" s="3"/>
+      <c r="E796" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F796" s="3"/>
       <c r="G796" s="3"/>
     </row>
@@ -12518,7 +12628,9 @@
       <c r="D797" s="3">
         <v>4200792</v>
       </c>
-      <c r="E797" s="3"/>
+      <c r="E797" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F797" s="3"/>
       <c r="G797" s="3"/>
     </row>
@@ -12535,7 +12647,9 @@
       <c r="D798" s="3">
         <v>4200793</v>
       </c>
-      <c r="E798" s="3"/>
+      <c r="E798" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F798" s="3"/>
       <c r="G798" s="3"/>
     </row>
@@ -12552,7 +12666,9 @@
       <c r="D799" s="3">
         <v>4200794</v>
       </c>
-      <c r="E799" s="3"/>
+      <c r="E799" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F799" s="3"/>
       <c r="G799" s="3"/>
     </row>
@@ -12569,7 +12685,9 @@
       <c r="D800" s="3">
         <v>4200795</v>
       </c>
-      <c r="E800" s="3"/>
+      <c r="E800" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F800" s="3"/>
       <c r="G800" s="3"/>
     </row>
@@ -12586,7 +12704,9 @@
       <c r="D801" s="3">
         <v>4200796</v>
       </c>
-      <c r="E801" s="3"/>
+      <c r="E801" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F801" s="3"/>
       <c r="G801" s="3"/>
     </row>
@@ -12603,7 +12723,9 @@
       <c r="D802" s="3">
         <v>4200797</v>
       </c>
-      <c r="E802" s="3"/>
+      <c r="E802" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F802" s="3"/>
       <c r="G802" s="3"/>
     </row>
@@ -12620,7 +12742,9 @@
       <c r="D803" s="3">
         <v>4200798</v>
       </c>
-      <c r="E803" s="3"/>
+      <c r="E803" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F803" s="3"/>
       <c r="G803" s="3"/>
     </row>
@@ -12637,7 +12761,9 @@
       <c r="D804" s="3">
         <v>4200799</v>
       </c>
-      <c r="E804" s="3"/>
+      <c r="E804" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F804" s="3"/>
       <c r="G804" s="3"/>
     </row>
@@ -12654,7 +12780,9 @@
       <c r="D805" s="3">
         <v>4200800</v>
       </c>
-      <c r="E805" s="3"/>
+      <c r="E805" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F805" s="3"/>
       <c r="G805" s="3"/>
     </row>

--- a/GHtoRB2_songids.xlsx
+++ b/GHtoRB2_songids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\RBDLC\reference\!GHtoRB2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DD2A12-D48E-4E86-B9C3-CBF6185B7A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927B1FA7-D988-401A-A2F7-66665292006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AE99FE45-D305-4219-A47C-654285C6D506}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="482">
   <si>
     <t>Last Updated: 3/13/26</t>
   </si>
@@ -732,9 +732,6 @@
     <t>Freezepop</t>
   </si>
   <si>
-    <t>Get Ready 2 Rokk</t>
-  </si>
-  <si>
     <t>Monkey Steals the Peach</t>
   </si>
   <si>
@@ -915,12 +912,6 @@
     <t>Toadies</t>
   </si>
   <si>
-    <t>Stop</t>
-  </si>
-  <si>
-    <t>Jane's Addiction</t>
-  </si>
-  <si>
     <t>YYZ</t>
   </si>
   <si>
@@ -997,6 +988,489 @@
   </si>
   <si>
     <t>You Should Be Ashamed Of Myself</t>
+  </si>
+  <si>
+    <t>GH6_dlc</t>
+  </si>
+  <si>
+    <t>Hunted Down</t>
+  </si>
+  <si>
+    <t>Soundgarden</t>
+  </si>
+  <si>
+    <t>Hands All Over</t>
+  </si>
+  <si>
+    <t>Outshined</t>
+  </si>
+  <si>
+    <t>Rusty Cage</t>
+  </si>
+  <si>
+    <t>Beyond The Life You Know</t>
+  </si>
+  <si>
+    <t>Darkest Hour</t>
+  </si>
+  <si>
+    <t>Doomsayer</t>
+  </si>
+  <si>
+    <t>Savor The Kill</t>
+  </si>
+  <si>
+    <t>Madina Lake</t>
+  </si>
+  <si>
+    <t>Hey Superstar</t>
+  </si>
+  <si>
+    <t>Across 5 Oceans</t>
+  </si>
+  <si>
+    <t>Middle Class Rut</t>
+  </si>
+  <si>
+    <t>Sad To Know</t>
+  </si>
+  <si>
+    <t>Lifelong Dayshift</t>
+  </si>
+  <si>
+    <t>New Low</t>
+  </si>
+  <si>
+    <t>Supermassive Black Hole</t>
+  </si>
+  <si>
+    <t>Sorrow</t>
+  </si>
+  <si>
+    <t>Bad Religion</t>
+  </si>
+  <si>
+    <t>Snow Patrol</t>
+  </si>
+  <si>
+    <t>Hands Open</t>
+  </si>
+  <si>
+    <t>Jet</t>
+  </si>
+  <si>
+    <t>She's A Genius</t>
+  </si>
+  <si>
+    <t>Headstrong</t>
+  </si>
+  <si>
+    <t>Trapt</t>
+  </si>
+  <si>
+    <t>Sic Transit Gloria... Glory Fades</t>
+  </si>
+  <si>
+    <t>Brand New</t>
+  </si>
+  <si>
+    <t>Puddle Of Mudd</t>
+  </si>
+  <si>
+    <t>Psycho</t>
+  </si>
+  <si>
+    <t>Little Sister</t>
+  </si>
+  <si>
+    <t>Queens Of The Stone Age</t>
+  </si>
+  <si>
+    <t>Saliva</t>
+  </si>
+  <si>
+    <t>Always</t>
+  </si>
+  <si>
+    <t>Black Sunday</t>
+  </si>
+  <si>
+    <t>Crazy Horse</t>
+  </si>
+  <si>
+    <t>Parade Of The Dead</t>
+  </si>
+  <si>
+    <t>Marilyn Manson</t>
+  </si>
+  <si>
+    <t>Tourniquet</t>
+  </si>
+  <si>
+    <t>Coma White</t>
+  </si>
+  <si>
+    <t>Get Your Gunn</t>
+  </si>
+  <si>
+    <t>Firewind</t>
+  </si>
+  <si>
+    <t>World On Fire</t>
+  </si>
+  <si>
+    <t>Children Of Bodom</t>
+  </si>
+  <si>
+    <t>Was It Worth It</t>
+  </si>
+  <si>
+    <t>Living Dead Beat</t>
+  </si>
+  <si>
+    <t>Blooddrunk</t>
+  </si>
+  <si>
+    <t>A Day To Remember</t>
+  </si>
+  <si>
+    <t>Downfall Of Us All</t>
+  </si>
+  <si>
+    <t>2nd Sucks</t>
+  </si>
+  <si>
+    <t>All I Want</t>
+  </si>
+  <si>
+    <t>Hawthorne Heights</t>
+  </si>
+  <si>
+    <t>Rescue Me</t>
+  </si>
+  <si>
+    <t>The Damned Things</t>
+  </si>
+  <si>
+    <t>We've Got A Situation Here</t>
+  </si>
+  <si>
+    <t>Buried Myself Alive</t>
+  </si>
+  <si>
+    <t>The Used</t>
+  </si>
+  <si>
+    <t>Nine Inch Nails</t>
+  </si>
+  <si>
+    <t>Head Like A Hole</t>
+  </si>
+  <si>
+    <t>Sponge</t>
+  </si>
+  <si>
+    <t>Plowed</t>
+  </si>
+  <si>
+    <t>Marcy Playground</t>
+  </si>
+  <si>
+    <t>Sex And Candy</t>
+  </si>
+  <si>
+    <t>What's The Frequency, Kenneth?</t>
+  </si>
+  <si>
+    <t>Real World</t>
+  </si>
+  <si>
+    <t>Matchbox Twenty</t>
+  </si>
+  <si>
+    <t>Goo Goo Dolls</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Bulletproof Heart</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>Love Song</t>
+  </si>
+  <si>
+    <t>Elected</t>
+  </si>
+  <si>
+    <t>Slash (w/ M. Shadows)</t>
+  </si>
+  <si>
+    <t>Nothing To Say</t>
+  </si>
+  <si>
+    <t>Slash (w/ Dave Grohl &amp; Duff McKagan)</t>
+  </si>
+  <si>
+    <t>Watch This</t>
+  </si>
+  <si>
+    <t>We're All Gonna Die</t>
+  </si>
+  <si>
+    <t>Slash (w/ Iggy Pop)</t>
+  </si>
+  <si>
+    <t>The Rocky Horror Picture Show</t>
+  </si>
+  <si>
+    <t>Hot Patootie</t>
+  </si>
+  <si>
+    <t>Sweet Transvestite</t>
+  </si>
+  <si>
+    <t>Linkin Park</t>
+  </si>
+  <si>
+    <t>Wretches And Kings</t>
+  </si>
+  <si>
+    <t>Blackout</t>
+  </si>
+  <si>
+    <t>Burning In The Skies</t>
+  </si>
+  <si>
+    <t>The Catalyst</t>
+  </si>
+  <si>
+    <t>The Messenger</t>
+  </si>
+  <si>
+    <t>Disturbed</t>
+  </si>
+  <si>
+    <t>The Infection</t>
+  </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>Birth Ritual</t>
+  </si>
+  <si>
+    <t>My Wave</t>
+  </si>
+  <si>
+    <t>Fell On Black Days</t>
+  </si>
+  <si>
+    <t>Burden In My Hand</t>
+  </si>
+  <si>
+    <t>Blow Up The Outside World</t>
+  </si>
+  <si>
+    <t>I Was Made For Lovin' You</t>
+  </si>
+  <si>
+    <t>KISS</t>
+  </si>
+  <si>
+    <t>Prodigal Son (Live)</t>
+  </si>
+  <si>
+    <t>You Gotta Move (Live)</t>
+  </si>
+  <si>
+    <t>Under My Thumb (Live)</t>
+  </si>
+  <si>
+    <t>I'm Free (Live)</t>
+  </si>
+  <si>
+    <t>Angels &amp; Airwaves</t>
+  </si>
+  <si>
+    <t>The Adventure</t>
+  </si>
+  <si>
+    <t>OK Go</t>
+  </si>
+  <si>
+    <t>A Million Ways</t>
+  </si>
+  <si>
+    <t>Counting Crows</t>
+  </si>
+  <si>
+    <t>Angels Of The Silences</t>
+  </si>
+  <si>
+    <t>Parachute</t>
+  </si>
+  <si>
+    <t>Back Again</t>
+  </si>
+  <si>
+    <t>The Bravery</t>
+  </si>
+  <si>
+    <t>Believe</t>
+  </si>
+  <si>
+    <t>LKT Tunstall</t>
+  </si>
+  <si>
+    <t>Black Horse And The Cherry Tree</t>
+  </si>
+  <si>
+    <t>Alphabeat</t>
+  </si>
+  <si>
+    <t>Fascination</t>
+  </si>
+  <si>
+    <t>The Airborne Toxic Event</t>
+  </si>
+  <si>
+    <t>Gasoline</t>
+  </si>
+  <si>
+    <t>Dashboard Confessional</t>
+  </si>
+  <si>
+    <t>Hands Down</t>
+  </si>
+  <si>
+    <t>Cold War Kids</t>
+  </si>
+  <si>
+    <t>Hang Me Up To Dry</t>
+  </si>
+  <si>
+    <t>The Turtles</t>
+  </si>
+  <si>
+    <t>Happy Together</t>
+  </si>
+  <si>
+    <t>Honky Tonk Women</t>
+  </si>
+  <si>
+    <t>Tonic</t>
+  </si>
+  <si>
+    <t>If You Could Only See ('09)</t>
+  </si>
+  <si>
+    <t>Marvin Gaye</t>
+  </si>
+  <si>
+    <t>I Heard It Through The Grapevine</t>
+  </si>
+  <si>
+    <t>Cheap Trick</t>
+  </si>
+  <si>
+    <t>I Want You To Want Me (Live)</t>
+  </si>
+  <si>
+    <t>Robbie Williams &amp; Kylie Minogue</t>
+  </si>
+  <si>
+    <t>Kids</t>
+  </si>
+  <si>
+    <t>Santigold</t>
+  </si>
+  <si>
+    <t>L.E.S. Artistes</t>
+  </si>
+  <si>
+    <t>Aly &amp; AJ</t>
+  </si>
+  <si>
+    <t>Like Whoa</t>
+  </si>
+  <si>
+    <t>Styx</t>
+  </si>
+  <si>
+    <t>Mr. Roboto</t>
+  </si>
+  <si>
+    <t>The Go-Go's</t>
+  </si>
+  <si>
+    <t>Our Lips Are Sealed</t>
+  </si>
+  <si>
+    <t>The Last Goodnight</t>
+  </si>
+  <si>
+    <t>Pictures Of You</t>
+  </si>
+  <si>
+    <t>Corinne Bailey Rae</t>
+  </si>
+  <si>
+    <t>Put Your Records On</t>
+  </si>
+  <si>
+    <t>N.E.R.D.</t>
+  </si>
+  <si>
+    <t>Rock Star</t>
+  </si>
+  <si>
+    <t>Everclear</t>
+  </si>
+  <si>
+    <t>Santa Monica</t>
+  </si>
+  <si>
+    <t>Hilary Duff</t>
+  </si>
+  <si>
+    <t>So Yesterday</t>
+  </si>
+  <si>
+    <t>Ben Harper &amp; The Innocent Criminals</t>
+  </si>
+  <si>
+    <t>Steal My Kisses</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Take A Picture</t>
+  </si>
+  <si>
+    <t>Take Back The City</t>
+  </si>
+  <si>
+    <t>Lily Allen</t>
+  </si>
+  <si>
+    <t>Take What You Take</t>
+  </si>
+  <si>
+    <t>Nelly Furtado</t>
+  </si>
+  <si>
+    <t>Turn Off The Light</t>
+  </si>
+  <si>
+    <t>Duffy</t>
+  </si>
+  <si>
+    <t>Warwick Avenue</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1998,7 @@
   <dimension ref="A1:G1515"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="1" max="1" width="32.21875" customWidth="1"/>
     <col min="2" max="2" width="35.5546875" customWidth="1"/>
     <col min="3" max="3" width="17.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" style="3" customWidth="1"/>
@@ -9783,41 +10257,59 @@
       <c r="G607" s="3"/>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A608" s="3"/>
-      <c r="B608" s="3"/>
+      <c r="A608" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B608" s="3" t="s">
+        <v>425</v>
+      </c>
       <c r="C608" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D608" s="3">
         <v>4200603</v>
       </c>
-      <c r="E608" s="3"/>
+      <c r="E608" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F608" s="3"/>
       <c r="G608" s="3"/>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A609" s="3"/>
-      <c r="B609" s="3"/>
+      <c r="A609" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>427</v>
+      </c>
       <c r="C609" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D609" s="3">
         <v>4200604</v>
       </c>
-      <c r="E609" s="3"/>
+      <c r="E609" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F609" s="3"/>
       <c r="G609" s="3"/>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A610" s="3"/>
-      <c r="B610" s="3"/>
+      <c r="A610" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>429</v>
+      </c>
       <c r="C610" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D610" s="3">
         <v>4200605</v>
       </c>
-      <c r="E610" s="3"/>
+      <c r="E610" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F610" s="3"/>
       <c r="G610" s="3"/>
     </row>
@@ -9854,15 +10346,21 @@
       <c r="G612" s="3"/>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A613" s="3"/>
-      <c r="B613" s="3"/>
+      <c r="A613" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="C613" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D613" s="3">
         <v>4200608</v>
       </c>
-      <c r="E613" s="3"/>
+      <c r="E613" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F613" s="3"/>
       <c r="G613" s="3"/>
     </row>
@@ -9886,15 +10384,21 @@
       <c r="G614" s="3"/>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A615" s="3"/>
-      <c r="B615" s="3"/>
+      <c r="A615" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>433</v>
+      </c>
       <c r="C615" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D615" s="3">
         <v>4200610</v>
       </c>
-      <c r="E615" s="3"/>
+      <c r="E615" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F615" s="3"/>
       <c r="G615" s="3"/>
     </row>
@@ -9990,106 +10494,154 @@
       <c r="G622" s="3"/>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A623" s="3"/>
-      <c r="B623" s="3"/>
+      <c r="A623" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>435</v>
+      </c>
       <c r="C623" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D623" s="3">
         <v>4200618</v>
       </c>
-      <c r="E623" s="3"/>
+      <c r="E623" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F623" s="3"/>
       <c r="G623" s="3"/>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A624" s="3"/>
-      <c r="B624" s="3"/>
+      <c r="A624" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>437</v>
+      </c>
       <c r="C624" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D624" s="3">
         <v>4200619</v>
       </c>
-      <c r="E624" s="3"/>
+      <c r="E624" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F624" s="3"/>
       <c r="G624" s="3"/>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A625" s="3"/>
-      <c r="B625" s="3"/>
+      <c r="A625" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>439</v>
+      </c>
       <c r="C625" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D625" s="3">
         <v>4200620</v>
       </c>
-      <c r="E625" s="3"/>
+      <c r="E625" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F625" s="3"/>
       <c r="G625" s="3"/>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A626" s="3"/>
-      <c r="B626" s="3"/>
+      <c r="A626" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>441</v>
+      </c>
       <c r="C626" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D626" s="3">
         <v>4200621</v>
       </c>
-      <c r="E626" s="3"/>
+      <c r="E626" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F626" s="3"/>
       <c r="G626" s="3"/>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A627" s="3"/>
-      <c r="B627" s="3"/>
+      <c r="A627" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>443</v>
+      </c>
       <c r="C627" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D627" s="3">
         <v>4200622</v>
       </c>
-      <c r="E627" s="3"/>
+      <c r="E627" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F627" s="3"/>
       <c r="G627" s="3"/>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A628" s="3"/>
-      <c r="B628" s="3"/>
+      <c r="A628" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>444</v>
+      </c>
       <c r="C628" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D628" s="3">
         <v>4200623</v>
       </c>
-      <c r="E628" s="3"/>
+      <c r="E628" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F628" s="3"/>
       <c r="G628" s="3"/>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A629" s="3"/>
-      <c r="B629" s="3"/>
+      <c r="A629" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>446</v>
+      </c>
       <c r="C629" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D629" s="3">
         <v>4200624</v>
       </c>
-      <c r="E629" s="3"/>
+      <c r="E629" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F629" s="3"/>
       <c r="G629" s="3"/>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A630" s="3"/>
-      <c r="B630" s="3"/>
+      <c r="A630" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>448</v>
+      </c>
       <c r="C630" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D630" s="3">
         <v>4200625</v>
       </c>
-      <c r="E630" s="3"/>
+      <c r="E630" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F630" s="3"/>
       <c r="G630" s="3"/>
     </row>
@@ -10107,15 +10659,21 @@
       <c r="G631" s="3"/>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A632" s="3"/>
-      <c r="B632" s="3"/>
+      <c r="A632" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>450</v>
+      </c>
       <c r="C632" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D632" s="3">
         <v>4200627</v>
       </c>
-      <c r="E632" s="3"/>
+      <c r="E632" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F632" s="3"/>
       <c r="G632" s="3"/>
     </row>
@@ -10133,15 +10691,21 @@
       <c r="G633" s="3"/>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A634" s="3"/>
-      <c r="B634" s="3"/>
+      <c r="A634" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="C634" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D634" s="3">
         <v>4200629</v>
       </c>
-      <c r="E634" s="3"/>
+      <c r="E634" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F634" s="3"/>
       <c r="G634" s="3"/>
     </row>
@@ -10159,15 +10723,21 @@
       <c r="G635" s="3"/>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A636" s="3"/>
-      <c r="B636" s="3"/>
+      <c r="A636" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>454</v>
+      </c>
       <c r="C636" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D636" s="3">
         <v>4200631</v>
       </c>
-      <c r="E636" s="3"/>
+      <c r="E636" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F636" s="3"/>
       <c r="G636" s="3"/>
     </row>
@@ -10198,15 +10768,21 @@
       <c r="G638" s="3"/>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A639" s="3"/>
-      <c r="B639" s="3"/>
+      <c r="A639" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>456</v>
+      </c>
       <c r="C639" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D639" s="3">
         <v>4200634</v>
       </c>
-      <c r="E639" s="3"/>
+      <c r="E639" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F639" s="3"/>
       <c r="G639" s="3"/>
     </row>
@@ -10256,15 +10832,21 @@
       <c r="G642" s="3"/>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A643" s="3"/>
-      <c r="B643" s="3"/>
+      <c r="A643" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>458</v>
+      </c>
       <c r="C643" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D643" s="3">
         <v>4200638</v>
       </c>
-      <c r="E643" s="3"/>
+      <c r="E643" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F643" s="3"/>
       <c r="G643" s="3"/>
     </row>
@@ -10295,15 +10877,21 @@
       <c r="G645" s="3"/>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A646" s="3"/>
-      <c r="B646" s="3"/>
+      <c r="A646" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>460</v>
+      </c>
       <c r="C646" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D646" s="3">
         <v>4200641</v>
       </c>
-      <c r="E646" s="3"/>
+      <c r="E646" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F646" s="3"/>
       <c r="G646" s="3"/>
     </row>
@@ -10321,15 +10909,21 @@
       <c r="G647" s="3"/>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A648" s="3"/>
-      <c r="B648" s="3"/>
+      <c r="A648" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>462</v>
+      </c>
       <c r="C648" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D648" s="3">
         <v>4200643</v>
       </c>
-      <c r="E648" s="3"/>
+      <c r="E648" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F648" s="3"/>
       <c r="G648" s="3"/>
     </row>
@@ -10366,15 +10960,21 @@
       <c r="G650" s="3"/>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A651" s="3"/>
-      <c r="B651" s="3"/>
+      <c r="A651" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>464</v>
+      </c>
       <c r="C651" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D651" s="3">
         <v>4200646</v>
       </c>
-      <c r="E651" s="3"/>
+      <c r="E651" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F651" s="3"/>
       <c r="G651" s="3"/>
     </row>
@@ -10392,28 +10992,40 @@
       <c r="G652" s="3"/>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A653" s="3"/>
-      <c r="B653" s="3"/>
+      <c r="A653" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>466</v>
+      </c>
       <c r="C653" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D653" s="3">
         <v>4200648</v>
       </c>
-      <c r="E653" s="3"/>
+      <c r="E653" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F653" s="3"/>
       <c r="G653" s="3"/>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A654" s="3"/>
-      <c r="B654" s="3"/>
+      <c r="A654" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>468</v>
+      </c>
       <c r="C654" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D654" s="3">
         <v>4200649</v>
       </c>
-      <c r="E654" s="3"/>
+      <c r="E654" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F654" s="3"/>
       <c r="G654" s="3"/>
     </row>
@@ -10444,28 +11056,40 @@
       <c r="G656" s="3"/>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A657" s="3"/>
-      <c r="B657" s="3"/>
+      <c r="A657" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>470</v>
+      </c>
       <c r="C657" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D657" s="3">
         <v>4200652</v>
       </c>
-      <c r="E657" s="3"/>
+      <c r="E657" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F657" s="3"/>
       <c r="G657" s="3"/>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A658" s="3"/>
-      <c r="B658" s="3"/>
+      <c r="A658" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>472</v>
+      </c>
       <c r="C658" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D658" s="3">
         <v>4200653</v>
       </c>
-      <c r="E658" s="3"/>
+      <c r="E658" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F658" s="3"/>
       <c r="G658" s="3"/>
     </row>
@@ -10483,54 +11107,78 @@
       <c r="G659" s="3"/>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A660" s="3"/>
-      <c r="B660" s="3"/>
+      <c r="A660" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>474</v>
+      </c>
       <c r="C660" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D660" s="3">
         <v>4200655</v>
       </c>
-      <c r="E660" s="3"/>
+      <c r="E660" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F660" s="3"/>
       <c r="G660" s="3"/>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A661" s="3"/>
-      <c r="B661" s="3"/>
+      <c r="A661" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>475</v>
+      </c>
       <c r="C661" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D661" s="3">
         <v>4200656</v>
       </c>
-      <c r="E661" s="3"/>
+      <c r="E661" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F661" s="3"/>
       <c r="G661" s="3"/>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A662" s="3"/>
-      <c r="B662" s="3"/>
+      <c r="A662" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>477</v>
+      </c>
       <c r="C662" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D662" s="3">
         <v>4200657</v>
       </c>
-      <c r="E662" s="3"/>
+      <c r="E662" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F662" s="3"/>
       <c r="G662" s="3"/>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A663" s="3"/>
-      <c r="B663" s="3"/>
+      <c r="A663" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>423</v>
+      </c>
       <c r="C663" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D663" s="3">
         <v>4200658</v>
       </c>
-      <c r="E663" s="3"/>
+      <c r="E663" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F663" s="3"/>
       <c r="G663" s="3"/>
     </row>
@@ -10548,15 +11196,21 @@
       <c r="G664" s="3"/>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A665" s="3"/>
-      <c r="B665" s="3"/>
+      <c r="A665" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>479</v>
+      </c>
       <c r="C665" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D665" s="3">
         <v>4200660</v>
       </c>
-      <c r="E665" s="3"/>
+      <c r="E665" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F665" s="3"/>
       <c r="G665" s="3"/>
     </row>
@@ -10593,15 +11247,21 @@
       <c r="G667" s="3"/>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A668" s="3"/>
-      <c r="B668" s="3"/>
+      <c r="A668" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="C668" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D668" s="3">
         <v>4200663</v>
       </c>
-      <c r="E668" s="3"/>
+      <c r="E668" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F668" s="3"/>
       <c r="G668" s="3"/>
     </row>
@@ -10619,43 +11279,43 @@
       <c r="G669" s="3"/>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A670" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B670" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="A670" s="3"/>
+      <c r="B670" s="3"/>
       <c r="C670" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D670" s="3">
         <v>4200665</v>
       </c>
-      <c r="E670" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E670" s="3"/>
       <c r="F670" s="3"/>
       <c r="G670" s="3"/>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A671" s="3"/>
-      <c r="B671" s="3"/>
+      <c r="A671" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="C671" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D671" s="3">
         <v>4200666</v>
       </c>
-      <c r="E671" s="3"/>
+      <c r="E671" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F671" s="3"/>
       <c r="G671" s="3"/>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C672" s="3" t="s">
         <v>95</v>
@@ -10702,9 +11362,7 @@
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
-      <c r="C675" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C675" s="3"/>
       <c r="D675" s="3">
         <v>4200670</v>
       </c>
@@ -10715,9 +11373,7 @@
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
-      <c r="C676" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C676" s="3"/>
       <c r="D676" s="3">
         <v>4200671</v>
       </c>
@@ -10728,9 +11384,7 @@
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
-      <c r="C677" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C677" s="3"/>
       <c r="D677" s="3">
         <v>4200672</v>
       </c>
@@ -10741,9 +11395,7 @@
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
-      <c r="C678" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C678" s="3"/>
       <c r="D678" s="3">
         <v>4200673</v>
       </c>
@@ -10754,9 +11406,7 @@
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
-      <c r="C679" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C679" s="3"/>
       <c r="D679" s="3">
         <v>4200674</v>
       </c>
@@ -10767,9 +11417,7 @@
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
-      <c r="C680" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C680" s="3"/>
       <c r="D680" s="3">
         <v>4200675</v>
       </c>
@@ -10780,9 +11428,7 @@
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
-      <c r="C681" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C681" s="3"/>
       <c r="D681" s="3">
         <v>4200676</v>
       </c>
@@ -10793,9 +11439,7 @@
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
-      <c r="C682" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C682" s="3"/>
       <c r="D682" s="3">
         <v>4200677</v>
       </c>
@@ -10806,9 +11450,7 @@
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
-      <c r="C683" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C683" s="3"/>
       <c r="D683" s="3">
         <v>4200678</v>
       </c>
@@ -10819,9 +11461,7 @@
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
-      <c r="C684" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C684" s="3"/>
       <c r="D684" s="3">
         <v>4200679</v>
       </c>
@@ -10832,9 +11472,7 @@
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
-      <c r="C685" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C685" s="3"/>
       <c r="D685" s="3">
         <v>4200680</v>
       </c>
@@ -10845,9 +11483,7 @@
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
-      <c r="C686" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C686" s="3"/>
       <c r="D686" s="3">
         <v>4200681</v>
       </c>
@@ -10858,9 +11494,7 @@
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
-      <c r="C687" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C687" s="3"/>
       <c r="D687" s="3">
         <v>4200682</v>
       </c>
@@ -10871,9 +11505,7 @@
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
-      <c r="C688" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C688" s="3"/>
       <c r="D688" s="3">
         <v>4200683</v>
       </c>
@@ -10884,9 +11516,7 @@
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
-      <c r="C689" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C689" s="3"/>
       <c r="D689" s="3">
         <v>4200684</v>
       </c>
@@ -10897,9 +11527,7 @@
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
-      <c r="C690" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C690" s="3"/>
       <c r="D690" s="3">
         <v>4200685</v>
       </c>
@@ -10910,9 +11538,7 @@
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
-      <c r="C691" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C691" s="3"/>
       <c r="D691" s="3">
         <v>4200686</v>
       </c>
@@ -10923,9 +11549,7 @@
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
-      <c r="C692" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C692" s="3"/>
       <c r="D692" s="3">
         <v>4200687</v>
       </c>
@@ -10936,9 +11560,7 @@
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
-      <c r="C693" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C693" s="3"/>
       <c r="D693" s="3">
         <v>4200688</v>
       </c>
@@ -10949,9 +11571,7 @@
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
-      <c r="C694" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C694" s="3"/>
       <c r="D694" s="3">
         <v>4200689</v>
       </c>
@@ -10962,9 +11582,7 @@
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
-      <c r="C695" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C695" s="3"/>
       <c r="D695" s="3">
         <v>4200690</v>
       </c>
@@ -10975,9 +11593,7 @@
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
-      <c r="C696" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C696" s="3"/>
       <c r="D696" s="3">
         <v>4200691</v>
       </c>
@@ -10988,9 +11604,7 @@
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
-      <c r="C697" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C697" s="3"/>
       <c r="D697" s="3">
         <v>4200692</v>
       </c>
@@ -11001,9 +11615,7 @@
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
-      <c r="C698" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C698" s="3"/>
       <c r="D698" s="3">
         <v>4200693</v>
       </c>
@@ -11014,9 +11626,7 @@
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
-      <c r="C699" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C699" s="3"/>
       <c r="D699" s="3">
         <v>4200694</v>
       </c>
@@ -11027,9 +11637,7 @@
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
-      <c r="C700" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C700" s="3"/>
       <c r="D700" s="3">
         <v>4200695</v>
       </c>
@@ -11040,9 +11648,7 @@
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
-      <c r="C701" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C701" s="3"/>
       <c r="D701" s="3">
         <v>4200696</v>
       </c>
@@ -11053,9 +11659,7 @@
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
-      <c r="C702" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C702" s="3"/>
       <c r="D702" s="3">
         <v>4200697</v>
       </c>
@@ -11066,9 +11670,7 @@
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
-      <c r="C703" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="C703" s="3"/>
       <c r="D703" s="3">
         <v>4200698</v>
       </c>
@@ -11077,52 +11679,36 @@
       <c r="G703" s="3"/>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A704" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B704" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C704" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="A704" s="3"/>
+      <c r="B704" s="3"/>
+      <c r="C704" s="3"/>
       <c r="D704" s="3">
         <v>4200699</v>
       </c>
-      <c r="E704" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E704" s="3"/>
       <c r="F704" s="3"/>
       <c r="G704" s="3"/>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A705" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B705" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C705" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="A705" s="3"/>
+      <c r="B705" s="3"/>
+      <c r="C705" s="3"/>
       <c r="D705" s="3">
         <v>4200700</v>
       </c>
-      <c r="E705" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E705" s="3"/>
       <c r="F705" s="3"/>
       <c r="G705" s="3"/>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="C706" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D706" s="3">
         <v>4200701</v>
@@ -11135,13 +11721,13 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="C707" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D707" s="3">
         <v>4200702</v>
@@ -11154,13 +11740,13 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
-        <v>219</v>
+        <v>323</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>220</v>
+        <v>325</v>
       </c>
       <c r="C708" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D708" s="3">
         <v>4200703</v>
@@ -11173,13 +11759,13 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
-        <v>221</v>
+        <v>323</v>
       </c>
       <c r="B709" s="3" t="s">
-        <v>222</v>
+        <v>326</v>
       </c>
       <c r="C709" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D709" s="3">
         <v>4200704</v>
@@ -11192,13 +11778,13 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
-        <v>223</v>
+        <v>323</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>224</v>
+        <v>411</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D710" s="3">
         <v>4200705</v>
@@ -11210,52 +11796,40 @@
       <c r="G710" s="3"/>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A711" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B711" s="3" t="s">
-        <v>226</v>
-      </c>
+      <c r="A711" s="3"/>
+      <c r="B711" s="3"/>
       <c r="C711" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D711" s="3">
         <v>4200706</v>
       </c>
-      <c r="E711" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E711" s="3"/>
       <c r="F711" s="3"/>
       <c r="G711" s="3"/>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A712" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B712" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="A712" s="3"/>
+      <c r="B712" s="3"/>
       <c r="C712" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D712" s="3">
         <v>4200707</v>
       </c>
-      <c r="E712" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E712" s="3"/>
       <c r="F712" s="3"/>
       <c r="G712" s="3"/>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="B713" s="3" t="s">
-        <v>230</v>
+        <v>412</v>
       </c>
       <c r="C713" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D713" s="3">
         <v>4200708</v>
@@ -11268,13 +11842,13 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
-        <v>60</v>
+        <v>323</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>231</v>
+        <v>413</v>
       </c>
       <c r="C714" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D714" s="3">
         <v>4200709</v>
@@ -11287,13 +11861,13 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
-        <v>232</v>
+        <v>323</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>233</v>
+        <v>414</v>
       </c>
       <c r="C715" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D715" s="3">
         <v>4200710</v>
@@ -11306,13 +11880,13 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="C716" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D716" s="3">
         <v>4200711</v>
@@ -11325,13 +11899,13 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="B717" s="3" t="s">
-        <v>237</v>
+        <v>410</v>
       </c>
       <c r="C717" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D717" s="3">
         <v>4200712</v>
@@ -11344,13 +11918,13 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="B718" s="3" t="s">
-        <v>239</v>
+        <v>409</v>
       </c>
       <c r="C718" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D718" s="3">
         <v>4200713</v>
@@ -11362,33 +11936,27 @@
       <c r="G718" s="3"/>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A719" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B719" s="3" t="s">
-        <v>241</v>
-      </c>
+      <c r="A719" s="3"/>
+      <c r="B719" s="3"/>
       <c r="C719" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D719" s="3">
         <v>4200714</v>
       </c>
-      <c r="E719" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E719" s="3"/>
       <c r="F719" s="3"/>
       <c r="G719" s="3"/>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
-        <v>242</v>
+        <v>402</v>
       </c>
       <c r="B720" s="3" t="s">
-        <v>243</v>
+        <v>404</v>
       </c>
       <c r="C720" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D720" s="3">
         <v>4200715</v>
@@ -11401,13 +11969,13 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
-        <v>245</v>
+        <v>402</v>
       </c>
       <c r="B721" s="3" t="s">
-        <v>246</v>
+        <v>405</v>
       </c>
       <c r="C721" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D721" s="3">
         <v>4200716</v>
@@ -11420,13 +11988,13 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="B722" s="3" t="s">
-        <v>248</v>
+        <v>406</v>
       </c>
       <c r="C722" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="D722" s="3">
         <v>4200717</v>
@@ -11439,13 +12007,13 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
-        <v>285</v>
+        <v>402</v>
       </c>
       <c r="B723" s="3" t="s">
-        <v>284</v>
+        <v>407</v>
       </c>
       <c r="C723" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D723" s="3">
         <v>4200718</v>
@@ -11457,33 +12025,27 @@
       <c r="G723" s="3"/>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A724" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B724" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="A724" s="3"/>
+      <c r="B724" s="3"/>
       <c r="C724" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D724" s="3">
         <v>4200719</v>
       </c>
-      <c r="E724" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E724" s="3"/>
       <c r="F724" s="3"/>
       <c r="G724" s="3"/>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
-        <v>288</v>
+        <v>402</v>
       </c>
       <c r="B725" s="3" t="s">
-        <v>289</v>
+        <v>403</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D725" s="3">
         <v>4200720</v>
@@ -11498,7 +12060,7 @@
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D726" s="3">
         <v>4200721</v>
@@ -11508,28 +12070,40 @@
       <c r="G726" s="3"/>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A727" s="3"/>
-      <c r="B727" s="3"/>
+      <c r="A727" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="C727" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D727" s="3">
         <v>4200722</v>
       </c>
-      <c r="E727" s="3"/>
+      <c r="E727" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F727" s="3"/>
       <c r="G727" s="3"/>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A728" s="3"/>
-      <c r="B728" s="3"/>
+      <c r="A728" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>400</v>
+      </c>
       <c r="C728" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D728" s="3">
         <v>4200723</v>
       </c>
-      <c r="E728" s="3"/>
+      <c r="E728" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F728" s="3"/>
       <c r="G728" s="3"/>
     </row>
@@ -11537,7 +12111,7 @@
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D729" s="3">
         <v>4200724</v>
@@ -11550,7 +12124,7 @@
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D730" s="3">
         <v>4200725</v>
@@ -11560,73 +12134,91 @@
       <c r="G730" s="3"/>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A731" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B731" s="3" t="s">
-        <v>290</v>
-      </c>
+      <c r="A731" s="3"/>
+      <c r="B731" s="3"/>
       <c r="C731" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D731" s="3">
         <v>4200726</v>
       </c>
-      <c r="E731" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E731" s="3"/>
       <c r="F731" s="3"/>
       <c r="G731" s="3"/>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A732" s="3"/>
-      <c r="B732" s="3"/>
+      <c r="A732" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="C732" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D732" s="3">
         <v>4200727</v>
       </c>
-      <c r="E732" s="3"/>
+      <c r="E732" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F732" s="3"/>
       <c r="G732" s="3"/>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A733" s="3"/>
-      <c r="B733" s="3"/>
+      <c r="A733" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B733" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="C733" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D733" s="3">
         <v>4200728</v>
       </c>
-      <c r="E733" s="3"/>
+      <c r="E733" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F733" s="3"/>
       <c r="G733" s="3"/>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A734" s="3"/>
-      <c r="B734" s="3"/>
+      <c r="A734" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B734" s="3" t="s">
+        <v>394</v>
+      </c>
       <c r="C734" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D734" s="3">
         <v>4200729</v>
       </c>
-      <c r="E734" s="3"/>
+      <c r="E734" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F734" s="3"/>
       <c r="G734" s="3"/>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A735" s="3"/>
-      <c r="B735" s="3"/>
+      <c r="A735" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B735" s="3" t="s">
+        <v>392</v>
+      </c>
       <c r="C735" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D735" s="3">
         <v>4200730</v>
       </c>
-      <c r="E735" s="3"/>
+      <c r="E735" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F735" s="3"/>
       <c r="G735" s="3"/>
     </row>
@@ -11634,7 +12226,7 @@
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D736" s="3">
         <v>4200731</v>
@@ -11647,7 +12239,7 @@
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D737" s="3">
         <v>4200732</v>
@@ -11657,47 +12249,53 @@
       <c r="G737" s="3"/>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A738" s="3"/>
-      <c r="B738" s="3"/>
+      <c r="A738" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="C738" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D738" s="3">
         <v>4200733</v>
       </c>
-      <c r="E738" s="3"/>
+      <c r="E738" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F738" s="3"/>
       <c r="G738" s="3"/>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A739" s="3"/>
-      <c r="B739" s="3"/>
+      <c r="A739" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="C739" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D739" s="3">
         <v>4200734</v>
       </c>
-      <c r="E739" s="3"/>
+      <c r="E739" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F739" s="3"/>
       <c r="G739" s="3"/>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A740" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B740" s="3" t="s">
-        <v>292</v>
-      </c>
+      <c r="A740" s="3"/>
+      <c r="B740" s="3"/>
       <c r="C740" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D740" s="3">
         <v>4200735</v>
       </c>
-      <c r="E740" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E740" s="3"/>
       <c r="F740" s="3"/>
       <c r="G740" s="3"/>
     </row>
@@ -11705,7 +12303,7 @@
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D741" s="3">
         <v>4200736</v>
@@ -11718,7 +12316,7 @@
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D742" s="3">
         <v>4200737</v>
@@ -11728,41 +12326,59 @@
       <c r="G742" s="3"/>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A743" s="3"/>
-      <c r="B743" s="3"/>
+      <c r="A743" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B743" s="3" t="s">
+        <v>388</v>
+      </c>
       <c r="C743" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D743" s="3">
         <v>4200738</v>
       </c>
-      <c r="E743" s="3"/>
+      <c r="E743" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F743" s="3"/>
       <c r="G743" s="3"/>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A744" s="3"/>
-      <c r="B744" s="3"/>
+      <c r="A744" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B744" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="C744" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D744" s="3">
         <v>4200739</v>
       </c>
-      <c r="E744" s="3"/>
+      <c r="E744" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F744" s="3"/>
       <c r="G744" s="3"/>
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A745" s="3"/>
-      <c r="B745" s="3"/>
+      <c r="A745" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B745" s="3" t="s">
+        <v>384</v>
+      </c>
       <c r="C745" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D745" s="3">
         <v>4200740</v>
       </c>
-      <c r="E745" s="3"/>
+      <c r="E745" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F745" s="3"/>
       <c r="G745" s="3"/>
     </row>
@@ -11770,7 +12386,7 @@
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D746" s="3">
         <v>4200741</v>
@@ -11780,28 +12396,40 @@
       <c r="G746" s="3"/>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A747" s="3"/>
-      <c r="B747" s="3"/>
+      <c r="A747" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B747" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="C747" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D747" s="3">
         <v>4200742</v>
       </c>
-      <c r="E747" s="3"/>
+      <c r="E747" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F747" s="3"/>
       <c r="G747" s="3"/>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A748" s="3"/>
-      <c r="B748" s="3"/>
+      <c r="A748" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="C748" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D748" s="3">
         <v>4200743</v>
       </c>
-      <c r="E748" s="3"/>
+      <c r="E748" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F748" s="3"/>
       <c r="G748" s="3"/>
     </row>
@@ -11809,7 +12437,7 @@
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D749" s="3">
         <v>4200744</v>
@@ -11819,21 +12447,15 @@
       <c r="G749" s="3"/>
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A750" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B750" s="3" t="s">
-        <v>294</v>
-      </c>
+      <c r="A750" s="3"/>
+      <c r="B750" s="3"/>
       <c r="C750" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D750" s="3">
         <v>4200745</v>
       </c>
-      <c r="E750" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E750" s="3"/>
       <c r="F750" s="3"/>
       <c r="G750" s="3"/>
     </row>
@@ -11841,7 +12463,7 @@
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D751" s="3">
         <v>4200746</v>
@@ -11854,7 +12476,7 @@
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D752" s="3">
         <v>4200747</v>
@@ -11867,7 +12489,7 @@
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D753" s="3">
         <v>4200748</v>
@@ -11877,53 +12499,71 @@
       <c r="G753" s="3"/>
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A754" s="3"/>
-      <c r="B754" s="3"/>
+      <c r="A754" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B754" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="C754" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D754" s="3">
         <v>4200749</v>
       </c>
-      <c r="E754" s="3"/>
+      <c r="E754" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F754" s="3"/>
       <c r="G754" s="3"/>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A755" s="3"/>
-      <c r="B755" s="3"/>
+      <c r="A755" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B755" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="C755" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D755" s="3">
         <v>4200750</v>
       </c>
-      <c r="E755" s="3"/>
+      <c r="E755" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F755" s="3"/>
       <c r="G755" s="3"/>
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A756" s="3"/>
-      <c r="B756" s="3"/>
+      <c r="A756" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B756" s="3" t="s">
+        <v>375</v>
+      </c>
       <c r="C756" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D756" s="3">
         <v>4200751</v>
       </c>
-      <c r="E756" s="3"/>
+      <c r="E756" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F756" s="3"/>
       <c r="G756" s="3"/>
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="B757" s="3" t="s">
-        <v>296</v>
+        <v>373</v>
       </c>
       <c r="C757" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D757" s="3">
         <v>4200752</v>
@@ -11938,7 +12578,7 @@
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D758" s="3">
         <v>4200753</v>
@@ -11948,131 +12588,185 @@
       <c r="G758" s="3"/>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A759" s="3"/>
-      <c r="B759" s="3"/>
+      <c r="A759" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B759" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="C759" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D759" s="3">
         <v>4200754</v>
       </c>
-      <c r="E759" s="3"/>
+      <c r="E759" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F759" s="3"/>
       <c r="G759" s="3"/>
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A760" s="3"/>
-      <c r="B760" s="3"/>
+      <c r="A760" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B760" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="C760" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D760" s="3">
         <v>4200755</v>
       </c>
-      <c r="E760" s="3"/>
+      <c r="E760" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F760" s="3"/>
       <c r="G760" s="3"/>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A761" s="3"/>
-      <c r="B761" s="3"/>
+      <c r="A761" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B761" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="C761" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D761" s="3">
         <v>4200756</v>
       </c>
-      <c r="E761" s="3"/>
+      <c r="E761" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F761" s="3"/>
       <c r="G761" s="3"/>
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A762" s="3"/>
-      <c r="B762" s="3"/>
+      <c r="A762" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B762" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="C762" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D762" s="3">
         <v>4200757</v>
       </c>
-      <c r="E762" s="3"/>
+      <c r="E762" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F762" s="3"/>
       <c r="G762" s="3"/>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A763" s="3"/>
-      <c r="B763" s="3"/>
+      <c r="A763" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B763" s="3" t="s">
+        <v>366</v>
+      </c>
       <c r="C763" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D763" s="3">
         <v>4200758</v>
       </c>
-      <c r="E763" s="3"/>
+      <c r="E763" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F763" s="3"/>
       <c r="G763" s="3"/>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A764" s="3"/>
-      <c r="B764" s="3"/>
+      <c r="A764" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B764" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="C764" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D764" s="3">
         <v>4200759</v>
       </c>
-      <c r="E764" s="3"/>
+      <c r="E764" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F764" s="3"/>
       <c r="G764" s="3"/>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A765" s="3"/>
-      <c r="B765" s="3"/>
+      <c r="A765" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B765" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="C765" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D765" s="3">
         <v>4200760</v>
       </c>
-      <c r="E765" s="3"/>
+      <c r="E765" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F765" s="3"/>
       <c r="G765" s="3"/>
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A766" s="3"/>
-      <c r="B766" s="3"/>
+      <c r="A766" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B766" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="C766" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D766" s="3">
         <v>4200761</v>
       </c>
-      <c r="E766" s="3"/>
+      <c r="E766" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F766" s="3"/>
       <c r="G766" s="3"/>
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A767" s="3"/>
-      <c r="B767" s="3"/>
+      <c r="A767" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B767" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="C767" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D767" s="3">
         <v>4200762</v>
       </c>
-      <c r="E767" s="3"/>
+      <c r="E767" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="F767" s="3"/>
       <c r="G767" s="3"/>
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
-        <v>302</v>
+        <v>358</v>
       </c>
       <c r="B768" s="3" t="s">
-        <v>301</v>
+        <v>359</v>
       </c>
       <c r="C768" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D768" s="3">
         <v>4200763</v>
@@ -12085,13 +12779,13 @@
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B769" s="3" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="C769" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D769" s="3">
         <v>4200764</v>
@@ -12104,13 +12798,13 @@
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="B770" s="3" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="C770" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D770" s="3">
         <v>4200765</v>
@@ -12123,13 +12817,13 @@
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
-        <v>223</v>
+        <v>60</v>
       </c>
       <c r="B771" s="3" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="C771" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D771" s="3">
         <v>4200766</v>
@@ -12142,13 +12836,13 @@
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="B772" s="3" t="s">
-        <v>250</v>
+        <v>354</v>
       </c>
       <c r="C772" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D772" s="3">
         <v>4200767</v>
@@ -12161,13 +12855,13 @@
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="B773" s="3" t="s">
-        <v>251</v>
+        <v>351</v>
       </c>
       <c r="C773" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D773" s="3">
         <v>4200768</v>
@@ -12180,13 +12874,13 @@
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="B774" s="3" t="s">
-        <v>19</v>
+        <v>350</v>
       </c>
       <c r="C774" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D774" s="3">
         <v>4200769</v>
@@ -12199,13 +12893,13 @@
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="B775" s="3" t="s">
-        <v>252</v>
+        <v>347</v>
       </c>
       <c r="C775" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D775" s="3">
         <v>4200770</v>
@@ -12218,13 +12912,13 @@
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
-        <v>273</v>
+        <v>346</v>
       </c>
       <c r="B776" s="3" t="s">
-        <v>253</v>
+        <v>345</v>
       </c>
       <c r="C776" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D776" s="3">
         <v>4200771</v>
@@ -12237,13 +12931,13 @@
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="B777" s="3" t="s">
-        <v>254</v>
+        <v>344</v>
       </c>
       <c r="C777" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D777" s="3">
         <v>4200772</v>
@@ -12256,13 +12950,13 @@
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="B778" s="3" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="C778" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D778" s="3">
         <v>4200773</v>
@@ -12275,13 +12969,13 @@
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="B779" s="3" t="s">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="C779" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D779" s="3">
         <v>4200774</v>
@@ -12293,33 +12987,27 @@
       <c r="G779" s="3"/>
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A780" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B780" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="A780" s="3"/>
+      <c r="B780" s="3"/>
       <c r="C780" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D780" s="3">
         <v>4200775</v>
       </c>
-      <c r="E780" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E780" s="3"/>
       <c r="F780" s="3"/>
       <c r="G780" s="3"/>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
-        <v>276</v>
+        <v>11</v>
       </c>
       <c r="B781" s="3" t="s">
-        <v>258</v>
+        <v>338</v>
       </c>
       <c r="C781" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D781" s="3">
         <v>4200776</v>
@@ -12332,13 +13020,13 @@
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="B782" s="3" t="s">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="C782" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D782" s="3">
         <v>4200777</v>
@@ -12351,13 +13039,13 @@
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="B783" s="3" t="s">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="C783" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D783" s="3">
         <v>4200778</v>
@@ -12370,13 +13058,13 @@
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="B784" s="3" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="C784" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D784" s="3">
         <v>4200779</v>
@@ -12388,128 +13076,92 @@
       <c r="G784" s="3"/>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A785" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B785" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="A785" s="3"/>
+      <c r="B785" s="3"/>
       <c r="C785" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D785" s="3">
         <v>4200780</v>
       </c>
-      <c r="E785" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E785" s="3"/>
       <c r="F785" s="3"/>
       <c r="G785" s="3"/>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A786" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B786" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="A786" s="3"/>
+      <c r="B786" s="3"/>
       <c r="C786" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D786" s="3">
         <v>4200781</v>
       </c>
-      <c r="E786" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E786" s="3"/>
       <c r="F786" s="3"/>
       <c r="G786" s="3"/>
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A787" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B787" s="3" t="s">
-        <v>264</v>
-      </c>
+      <c r="A787" s="3"/>
+      <c r="B787" s="3"/>
       <c r="C787" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D787" s="3">
         <v>4200782</v>
       </c>
-      <c r="E787" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E787" s="3"/>
       <c r="F787" s="3"/>
       <c r="G787" s="3"/>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A788" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B788" s="3" t="s">
-        <v>265</v>
-      </c>
+      <c r="A788" s="3"/>
+      <c r="B788" s="3"/>
       <c r="C788" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D788" s="3">
         <v>4200783</v>
       </c>
-      <c r="E788" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E788" s="3"/>
       <c r="F788" s="3"/>
       <c r="G788" s="3"/>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A789" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B789" s="3" t="s">
-        <v>266</v>
-      </c>
+      <c r="A789" s="3"/>
+      <c r="B789" s="3"/>
       <c r="C789" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D789" s="3">
         <v>4200784</v>
       </c>
-      <c r="E789" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E789" s="3"/>
       <c r="F789" s="3"/>
       <c r="G789" s="3"/>
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A790" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B790" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="A790" s="3"/>
+      <c r="B790" s="3"/>
       <c r="C790" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D790" s="3">
         <v>4200785</v>
       </c>
-      <c r="E790" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E790" s="3"/>
       <c r="F790" s="3"/>
       <c r="G790" s="3"/>
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A791" s="3" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="B791" s="3" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="C791" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D791" s="3">
         <v>4200786</v>
@@ -12522,13 +13174,13 @@
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A792" s="3" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="B792" s="3" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="C792" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D792" s="3">
         <v>4200787</v>
@@ -12541,13 +13193,13 @@
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A793" s="3" t="s">
-        <v>270</v>
+        <v>328</v>
       </c>
       <c r="B793" s="3" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="C793" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D793" s="3">
         <v>4200788</v>
@@ -12560,13 +13212,13 @@
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A794" s="3" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="B794" s="3" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C794" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D794" s="3">
         <v>4200789</v>
@@ -12579,13 +13231,13 @@
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A795" s="3" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="B795" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C795" s="3" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="D795" s="3">
         <v>4200790</v>
@@ -12597,192 +13249,112 @@
       <c r="G795" s="3"/>
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A796" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B796" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C796" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A796" s="3"/>
+      <c r="B796" s="3"/>
+      <c r="C796" s="3"/>
       <c r="D796" s="3">
         <v>4200791</v>
       </c>
-      <c r="E796" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E796" s="3"/>
       <c r="F796" s="3"/>
       <c r="G796" s="3"/>
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A797" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B797" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C797" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A797" s="3"/>
+      <c r="B797" s="3"/>
+      <c r="C797" s="3"/>
       <c r="D797" s="3">
         <v>4200792</v>
       </c>
-      <c r="E797" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E797" s="3"/>
       <c r="F797" s="3"/>
       <c r="G797" s="3"/>
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A798" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B798" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C798" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A798" s="3"/>
+      <c r="B798" s="3"/>
+      <c r="C798" s="3"/>
       <c r="D798" s="3">
         <v>4200793</v>
       </c>
-      <c r="E798" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E798" s="3"/>
       <c r="F798" s="3"/>
       <c r="G798" s="3"/>
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A799" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B799" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C799" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A799" s="3"/>
+      <c r="B799" s="3"/>
+      <c r="C799" s="3"/>
       <c r="D799" s="3">
         <v>4200794</v>
       </c>
-      <c r="E799" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E799" s="3"/>
       <c r="F799" s="3"/>
       <c r="G799" s="3"/>
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A800" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B800" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C800" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A800" s="3"/>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3"/>
       <c r="D800" s="3">
         <v>4200795</v>
       </c>
-      <c r="E800" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E800" s="3"/>
       <c r="F800" s="3"/>
       <c r="G800" s="3"/>
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A801" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B801" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C801" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A801" s="3"/>
+      <c r="B801" s="3"/>
+      <c r="C801" s="3"/>
       <c r="D801" s="3">
         <v>4200796</v>
       </c>
-      <c r="E801" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E801" s="3"/>
       <c r="F801" s="3"/>
       <c r="G801" s="3"/>
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A802" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B802" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C802" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A802" s="3"/>
+      <c r="B802" s="3"/>
+      <c r="C802" s="3"/>
       <c r="D802" s="3">
         <v>4200797</v>
       </c>
-      <c r="E802" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E802" s="3"/>
       <c r="F802" s="3"/>
       <c r="G802" s="3"/>
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A803" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B803" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C803" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A803" s="3"/>
+      <c r="B803" s="3"/>
+      <c r="C803" s="3"/>
       <c r="D803" s="3">
         <v>4200798</v>
       </c>
-      <c r="E803" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E803" s="3"/>
       <c r="F803" s="3"/>
       <c r="G803" s="3"/>
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A804" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B804" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C804" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A804" s="3"/>
+      <c r="B804" s="3"/>
+      <c r="C804" s="3"/>
       <c r="D804" s="3">
         <v>4200799</v>
       </c>
-      <c r="E804" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E804" s="3"/>
       <c r="F804" s="3"/>
       <c r="G804" s="3"/>
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A805" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B805" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C805" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A805" s="3"/>
+      <c r="B805" s="3"/>
+      <c r="C805" s="3"/>
       <c r="D805" s="3">
         <v>4200800</v>
       </c>
-      <c r="E805" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E805" s="3"/>
       <c r="F805" s="3"/>
       <c r="G805" s="3"/>
     </row>
@@ -12800,7 +13372,9 @@
     <row r="807" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
-      <c r="C807" s="3"/>
+      <c r="C807" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D807" s="3">
         <v>4200802</v>
       </c>
@@ -12811,7 +13385,9 @@
     <row r="808" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
-      <c r="C808" s="3"/>
+      <c r="C808" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D808" s="3">
         <v>4200803</v>
       </c>
@@ -12822,7 +13398,9 @@
     <row r="809" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
-      <c r="C809" s="3"/>
+      <c r="C809" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D809" s="3">
         <v>4200804</v>
       </c>
@@ -12833,7 +13411,9 @@
     <row r="810" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
-      <c r="C810" s="3"/>
+      <c r="C810" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D810" s="3">
         <v>4200805</v>
       </c>
@@ -12844,7 +13424,9 @@
     <row r="811" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
-      <c r="C811" s="3"/>
+      <c r="C811" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D811" s="3">
         <v>4200806</v>
       </c>
@@ -12855,7 +13437,9 @@
     <row r="812" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
-      <c r="C812" s="3"/>
+      <c r="C812" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D812" s="3">
         <v>4200807</v>
       </c>
@@ -12866,7 +13450,9 @@
     <row r="813" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
-      <c r="C813" s="3"/>
+      <c r="C813" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D813" s="3">
         <v>4200808</v>
       </c>
@@ -12877,7 +13463,9 @@
     <row r="814" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
-      <c r="C814" s="3"/>
+      <c r="C814" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D814" s="3">
         <v>4200809</v>
       </c>
@@ -12888,7 +13476,9 @@
     <row r="815" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
-      <c r="C815" s="3"/>
+      <c r="C815" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D815" s="3">
         <v>4200810</v>
       </c>
@@ -12899,7 +13489,9 @@
     <row r="816" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
-      <c r="C816" s="3"/>
+      <c r="C816" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D816" s="3">
         <v>4200811</v>
       </c>
@@ -12910,7 +13502,9 @@
     <row r="817" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
-      <c r="C817" s="3"/>
+      <c r="C817" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D817" s="3">
         <v>4200812</v>
       </c>
@@ -12921,7 +13515,9 @@
     <row r="818" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
-      <c r="C818" s="3"/>
+      <c r="C818" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D818" s="3">
         <v>4200813</v>
       </c>
@@ -12932,7 +13528,9 @@
     <row r="819" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
-      <c r="C819" s="3"/>
+      <c r="C819" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D819" s="3">
         <v>4200814</v>
       </c>
@@ -12943,7 +13541,9 @@
     <row r="820" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
-      <c r="C820" s="3"/>
+      <c r="C820" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D820" s="3">
         <v>4200815</v>
       </c>
@@ -12954,7 +13554,9 @@
     <row r="821" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
-      <c r="C821" s="3"/>
+      <c r="C821" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D821" s="3">
         <v>4200816</v>
       </c>
@@ -12965,7 +13567,9 @@
     <row r="822" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
-      <c r="C822" s="3"/>
+      <c r="C822" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D822" s="3">
         <v>4200817</v>
       </c>
@@ -12976,7 +13580,9 @@
     <row r="823" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
-      <c r="C823" s="3"/>
+      <c r="C823" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D823" s="3">
         <v>4200818</v>
       </c>
@@ -12987,7 +13593,9 @@
     <row r="824" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
-      <c r="C824" s="3"/>
+      <c r="C824" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D824" s="3">
         <v>4200819</v>
       </c>
@@ -12998,7 +13606,9 @@
     <row r="825" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
-      <c r="C825" s="3"/>
+      <c r="C825" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D825" s="3">
         <v>4200820</v>
       </c>
@@ -13009,7 +13619,9 @@
     <row r="826" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
-      <c r="C826" s="3"/>
+      <c r="C826" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D826" s="3">
         <v>4200821</v>
       </c>
@@ -13020,7 +13632,9 @@
     <row r="827" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
-      <c r="C827" s="3"/>
+      <c r="C827" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D827" s="3">
         <v>4200822</v>
       </c>
@@ -13031,7 +13645,9 @@
     <row r="828" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
-      <c r="C828" s="3"/>
+      <c r="C828" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D828" s="3">
         <v>4200823</v>
       </c>
@@ -13042,7 +13658,9 @@
     <row r="829" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
-      <c r="C829" s="3"/>
+      <c r="C829" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D829" s="3">
         <v>4200824</v>
       </c>
@@ -13053,7 +13671,9 @@
     <row r="830" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
-      <c r="C830" s="3"/>
+      <c r="C830" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D830" s="3">
         <v>4200825</v>
       </c>
@@ -13064,7 +13684,9 @@
     <row r="831" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
-      <c r="C831" s="3"/>
+      <c r="C831" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D831" s="3">
         <v>4200826</v>
       </c>
@@ -13075,7 +13697,9 @@
     <row r="832" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
-      <c r="C832" s="3"/>
+      <c r="C832" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D832" s="3">
         <v>4200827</v>
       </c>
@@ -13086,7 +13710,9 @@
     <row r="833" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
-      <c r="C833" s="3"/>
+      <c r="C833" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D833" s="3">
         <v>4200828</v>
       </c>
@@ -13097,7 +13723,9 @@
     <row r="834" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
-      <c r="C834" s="3"/>
+      <c r="C834" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D834" s="3">
         <v>4200829</v>
       </c>
@@ -13108,7 +13736,9 @@
     <row r="835" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
-      <c r="C835" s="3"/>
+      <c r="C835" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D835" s="3">
         <v>4200830</v>
       </c>
@@ -13117,9 +13747,15 @@
       <c r="G835" s="3"/>
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A836" s="3"/>
-      <c r="B836" s="3"/>
-      <c r="C836" s="3"/>
+      <c r="A836" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B836" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C836" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D836" s="3">
         <v>4200831</v>
       </c>
@@ -13128,9 +13764,15 @@
       <c r="G836" s="3"/>
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A837" s="3"/>
-      <c r="B837" s="3"/>
-      <c r="C837" s="3"/>
+      <c r="A837" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B837" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C837" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D837" s="3">
         <v>4200832</v>
       </c>
@@ -13139,9 +13781,15 @@
       <c r="G837" s="3"/>
     </row>
     <row r="838" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A838" s="3"/>
-      <c r="B838" s="3"/>
-      <c r="C838" s="3"/>
+      <c r="A838" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B838" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C838" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D838" s="3">
         <v>4200833</v>
       </c>
@@ -13150,9 +13798,15 @@
       <c r="G838" s="3"/>
     </row>
     <row r="839" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A839" s="3"/>
-      <c r="B839" s="3"/>
-      <c r="C839" s="3"/>
+      <c r="A839" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B839" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C839" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D839" s="3">
         <v>4200834</v>
       </c>
@@ -13161,9 +13815,15 @@
       <c r="G839" s="3"/>
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A840" s="3"/>
-      <c r="B840" s="3"/>
-      <c r="C840" s="3"/>
+      <c r="A840" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B840" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C840" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D840" s="3">
         <v>4200835</v>
       </c>
@@ -13172,9 +13832,15 @@
       <c r="G840" s="3"/>
     </row>
     <row r="841" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A841" s="3"/>
-      <c r="B841" s="3"/>
-      <c r="C841" s="3"/>
+      <c r="A841" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B841" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C841" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D841" s="3">
         <v>4200836</v>
       </c>
@@ -13183,9 +13849,15 @@
       <c r="G841" s="3"/>
     </row>
     <row r="842" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A842" s="3"/>
-      <c r="B842" s="3"/>
-      <c r="C842" s="3"/>
+      <c r="A842" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B842" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C842" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D842" s="3">
         <v>4200837</v>
       </c>
@@ -13194,9 +13866,15 @@
       <c r="G842" s="3"/>
     </row>
     <row r="843" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A843" s="3"/>
-      <c r="B843" s="3"/>
-      <c r="C843" s="3"/>
+      <c r="A843" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B843" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C843" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D843" s="3">
         <v>4200838</v>
       </c>
@@ -13205,9 +13883,15 @@
       <c r="G843" s="3"/>
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A844" s="3"/>
-      <c r="B844" s="3"/>
-      <c r="C844" s="3"/>
+      <c r="A844" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B844" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C844" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D844" s="3">
         <v>4200839</v>
       </c>
@@ -13216,9 +13900,15 @@
       <c r="G844" s="3"/>
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A845" s="3"/>
-      <c r="B845" s="3"/>
-      <c r="C845" s="3"/>
+      <c r="A845" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B845" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C845" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D845" s="3">
         <v>4200840</v>
       </c>
@@ -13227,9 +13917,15 @@
       <c r="G845" s="3"/>
     </row>
     <row r="846" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A846" s="3"/>
-      <c r="B846" s="3"/>
-      <c r="C846" s="3"/>
+      <c r="A846" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B846" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C846" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D846" s="3">
         <v>4200841</v>
       </c>
@@ -13238,9 +13934,15 @@
       <c r="G846" s="3"/>
     </row>
     <row r="847" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A847" s="3"/>
-      <c r="B847" s="3"/>
-      <c r="C847" s="3"/>
+      <c r="A847" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B847" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C847" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D847" s="3">
         <v>4200842</v>
       </c>
@@ -13251,7 +13953,9 @@
     <row r="848" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
-      <c r="C848" s="3"/>
+      <c r="C848" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D848" s="3">
         <v>4200843</v>
       </c>
@@ -13260,9 +13964,15 @@
       <c r="G848" s="3"/>
     </row>
     <row r="849" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A849" s="3"/>
-      <c r="B849" s="3"/>
-      <c r="C849" s="3"/>
+      <c r="A849" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B849" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C849" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D849" s="3">
         <v>4200844</v>
       </c>
@@ -13271,9 +13981,15 @@
       <c r="G849" s="3"/>
     </row>
     <row r="850" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A850" s="3"/>
-      <c r="B850" s="3"/>
-      <c r="C850" s="3"/>
+      <c r="A850" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B850" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C850" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D850" s="3">
         <v>4200845</v>
       </c>
@@ -13282,9 +13998,15 @@
       <c r="G850" s="3"/>
     </row>
     <row r="851" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A851" s="3"/>
-      <c r="B851" s="3"/>
-      <c r="C851" s="3"/>
+      <c r="A851" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B851" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C851" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D851" s="3">
         <v>4200846</v>
       </c>
@@ -13293,9 +14015,15 @@
       <c r="G851" s="3"/>
     </row>
     <row r="852" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A852" s="3"/>
-      <c r="B852" s="3"/>
-      <c r="C852" s="3"/>
+      <c r="A852" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B852" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C852" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D852" s="3">
         <v>4200847</v>
       </c>
@@ -13304,9 +14032,15 @@
       <c r="G852" s="3"/>
     </row>
     <row r="853" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A853" s="3"/>
-      <c r="B853" s="3"/>
-      <c r="C853" s="3"/>
+      <c r="A853" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B853" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C853" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D853" s="3">
         <v>4200848</v>
       </c>
@@ -13315,9 +14049,15 @@
       <c r="G853" s="3"/>
     </row>
     <row r="854" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A854" s="3"/>
-      <c r="B854" s="3"/>
-      <c r="C854" s="3"/>
+      <c r="A854" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B854" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C854" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="D854" s="3">
         <v>4200849</v>
       </c>
@@ -13326,9 +14066,15 @@
       <c r="G854" s="3"/>
     </row>
     <row r="855" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A855" s="3"/>
-      <c r="B855" s="3"/>
-      <c r="C855" s="3"/>
+      <c r="A855" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B855" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C855" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D855" s="3">
         <v>4200850</v>
       </c>
@@ -13337,9 +14083,15 @@
       <c r="G855" s="3"/>
     </row>
     <row r="856" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A856" s="3"/>
-      <c r="B856" s="3"/>
-      <c r="C856" s="3"/>
+      <c r="A856" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B856" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C856" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D856" s="3">
         <v>4200851</v>
       </c>
@@ -13348,9 +14100,15 @@
       <c r="G856" s="3"/>
     </row>
     <row r="857" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A857" s="3"/>
-      <c r="B857" s="3"/>
-      <c r="C857" s="3"/>
+      <c r="A857" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B857" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C857" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D857" s="3">
         <v>4200852</v>
       </c>
@@ -13361,7 +14119,9 @@
     <row r="858" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
-      <c r="C858" s="3"/>
+      <c r="C858" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D858" s="3">
         <v>4200853</v>
       </c>
@@ -13372,7 +14132,9 @@
     <row r="859" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
-      <c r="C859" s="3"/>
+      <c r="C859" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D859" s="3">
         <v>4200854</v>
       </c>
@@ -13383,7 +14145,9 @@
     <row r="860" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
-      <c r="C860" s="3"/>
+      <c r="C860" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D860" s="3">
         <v>4200855</v>
       </c>
@@ -13394,7 +14158,9 @@
     <row r="861" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
-      <c r="C861" s="3"/>
+      <c r="C861" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D861" s="3">
         <v>4200856</v>
       </c>
@@ -13405,7 +14171,9 @@
     <row r="862" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
-      <c r="C862" s="3"/>
+      <c r="C862" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D862" s="3">
         <v>4200857</v>
       </c>
@@ -13414,9 +14182,15 @@
       <c r="G862" s="3"/>
     </row>
     <row r="863" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A863" s="3"/>
-      <c r="B863" s="3"/>
-      <c r="C863" s="3"/>
+      <c r="A863" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B863" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C863" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D863" s="3">
         <v>4200858</v>
       </c>
@@ -13427,7 +14201,9 @@
     <row r="864" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
-      <c r="C864" s="3"/>
+      <c r="C864" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D864" s="3">
         <v>4200859</v>
       </c>
@@ -13438,7 +14214,9 @@
     <row r="865" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
-      <c r="C865" s="3"/>
+      <c r="C865" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D865" s="3">
         <v>4200860</v>
       </c>
@@ -13449,7 +14227,9 @@
     <row r="866" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
-      <c r="C866" s="3"/>
+      <c r="C866" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D866" s="3">
         <v>4200861</v>
       </c>
@@ -13460,7 +14240,9 @@
     <row r="867" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
-      <c r="C867" s="3"/>
+      <c r="C867" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D867" s="3">
         <v>4200862</v>
       </c>
@@ -13471,7 +14253,9 @@
     <row r="868" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
-      <c r="C868" s="3"/>
+      <c r="C868" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D868" s="3">
         <v>4200863</v>
       </c>
@@ -13482,7 +14266,9 @@
     <row r="869" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
-      <c r="C869" s="3"/>
+      <c r="C869" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D869" s="3">
         <v>4200864</v>
       </c>
@@ -13493,7 +14279,9 @@
     <row r="870" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
-      <c r="C870" s="3"/>
+      <c r="C870" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D870" s="3">
         <v>4200865</v>
       </c>
@@ -13504,7 +14292,9 @@
     <row r="871" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
-      <c r="C871" s="3"/>
+      <c r="C871" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D871" s="3">
         <v>4200866</v>
       </c>
@@ -13513,9 +14303,15 @@
       <c r="G871" s="3"/>
     </row>
     <row r="872" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A872" s="3"/>
-      <c r="B872" s="3"/>
-      <c r="C872" s="3"/>
+      <c r="A872" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B872" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C872" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D872" s="3">
         <v>4200867</v>
       </c>
@@ -13526,7 +14322,9 @@
     <row r="873" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
-      <c r="C873" s="3"/>
+      <c r="C873" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D873" s="3">
         <v>4200868</v>
       </c>
@@ -13537,7 +14335,9 @@
     <row r="874" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
-      <c r="C874" s="3"/>
+      <c r="C874" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D874" s="3">
         <v>4200869</v>
       </c>
@@ -13548,7 +14348,9 @@
     <row r="875" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
-      <c r="C875" s="3"/>
+      <c r="C875" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D875" s="3">
         <v>4200870</v>
       </c>
@@ -13559,7 +14361,9 @@
     <row r="876" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
-      <c r="C876" s="3"/>
+      <c r="C876" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D876" s="3">
         <v>4200871</v>
       </c>
@@ -13570,7 +14374,9 @@
     <row r="877" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
-      <c r="C877" s="3"/>
+      <c r="C877" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D877" s="3">
         <v>4200872</v>
       </c>
@@ -13581,7 +14387,9 @@
     <row r="878" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
-      <c r="C878" s="3"/>
+      <c r="C878" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D878" s="3">
         <v>4200873</v>
       </c>
@@ -13592,7 +14400,9 @@
     <row r="879" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
-      <c r="C879" s="3"/>
+      <c r="C879" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D879" s="3">
         <v>4200874</v>
       </c>
@@ -13603,7 +14413,9 @@
     <row r="880" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
-      <c r="C880" s="3"/>
+      <c r="C880" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D880" s="3">
         <v>4200875</v>
       </c>
@@ -13614,7 +14426,9 @@
     <row r="881" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
-      <c r="C881" s="3"/>
+      <c r="C881" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D881" s="3">
         <v>4200876</v>
       </c>
@@ -13623,9 +14437,15 @@
       <c r="G881" s="3"/>
     </row>
     <row r="882" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A882" s="3"/>
-      <c r="B882" s="3"/>
-      <c r="C882" s="3"/>
+      <c r="A882" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B882" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C882" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D882" s="3">
         <v>4200877</v>
       </c>
@@ -13636,7 +14456,9 @@
     <row r="883" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
-      <c r="C883" s="3"/>
+      <c r="C883" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D883" s="3">
         <v>4200878</v>
       </c>
@@ -13647,7 +14469,9 @@
     <row r="884" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
-      <c r="C884" s="3"/>
+      <c r="C884" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D884" s="3">
         <v>4200879</v>
       </c>
@@ -13658,7 +14482,9 @@
     <row r="885" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
-      <c r="C885" s="3"/>
+      <c r="C885" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D885" s="3">
         <v>4200880</v>
       </c>
@@ -13669,7 +14495,9 @@
     <row r="886" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
-      <c r="C886" s="3"/>
+      <c r="C886" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D886" s="3">
         <v>4200881</v>
       </c>
@@ -13680,7 +14508,9 @@
     <row r="887" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
-      <c r="C887" s="3"/>
+      <c r="C887" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D887" s="3">
         <v>4200882</v>
       </c>
@@ -13691,7 +14521,9 @@
     <row r="888" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
-      <c r="C888" s="3"/>
+      <c r="C888" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D888" s="3">
         <v>4200883</v>
       </c>
@@ -13702,7 +14534,9 @@
     <row r="889" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
-      <c r="C889" s="3"/>
+      <c r="C889" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D889" s="3">
         <v>4200884</v>
       </c>
@@ -13713,7 +14547,9 @@
     <row r="890" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
-      <c r="C890" s="3"/>
+      <c r="C890" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D890" s="3">
         <v>4200885</v>
       </c>
@@ -13724,7 +14560,9 @@
     <row r="891" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
-      <c r="C891" s="3"/>
+      <c r="C891" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D891" s="3">
         <v>4200886</v>
       </c>
@@ -13735,7 +14573,9 @@
     <row r="892" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
-      <c r="C892" s="3"/>
+      <c r="C892" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D892" s="3">
         <v>4200887</v>
       </c>
@@ -13746,7 +14586,9 @@
     <row r="893" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
-      <c r="C893" s="3"/>
+      <c r="C893" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D893" s="3">
         <v>4200888</v>
       </c>
@@ -13757,7 +14599,9 @@
     <row r="894" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
-      <c r="C894" s="3"/>
+      <c r="C894" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D894" s="3">
         <v>4200889</v>
       </c>
@@ -13768,7 +14612,9 @@
     <row r="895" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
-      <c r="C895" s="3"/>
+      <c r="C895" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D895" s="3">
         <v>4200890</v>
       </c>
@@ -13779,7 +14625,9 @@
     <row r="896" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
-      <c r="C896" s="3"/>
+      <c r="C896" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D896" s="3">
         <v>4200891</v>
       </c>
@@ -13790,7 +14638,9 @@
     <row r="897" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
-      <c r="C897" s="3"/>
+      <c r="C897" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D897" s="3">
         <v>4200892</v>
       </c>
@@ -13801,7 +14651,9 @@
     <row r="898" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
-      <c r="C898" s="3"/>
+      <c r="C898" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D898" s="3">
         <v>4200893</v>
       </c>
@@ -13812,7 +14664,9 @@
     <row r="899" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
-      <c r="C899" s="3"/>
+      <c r="C899" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D899" s="3">
         <v>4200894</v>
       </c>
@@ -13821,9 +14675,15 @@
       <c r="G899" s="3"/>
     </row>
     <row r="900" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A900" s="3"/>
-      <c r="B900" s="3"/>
-      <c r="C900" s="3"/>
+      <c r="A900" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B900" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C900" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D900" s="3">
         <v>4200895</v>
       </c>
@@ -13832,9 +14692,15 @@
       <c r="G900" s="3"/>
     </row>
     <row r="901" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A901" s="3"/>
-      <c r="B901" s="3"/>
-      <c r="C901" s="3"/>
+      <c r="A901" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B901" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C901" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D901" s="3">
         <v>4200896</v>
       </c>
@@ -13843,9 +14709,15 @@
       <c r="G901" s="3"/>
     </row>
     <row r="902" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A902" s="3"/>
-      <c r="B902" s="3"/>
-      <c r="C902" s="3"/>
+      <c r="A902" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B902" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C902" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D902" s="3">
         <v>4200897</v>
       </c>
@@ -13854,9 +14726,15 @@
       <c r="G902" s="3"/>
     </row>
     <row r="903" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A903" s="3"/>
-      <c r="B903" s="3"/>
-      <c r="C903" s="3"/>
+      <c r="A903" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B903" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C903" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D903" s="3">
         <v>4200898</v>
       </c>
@@ -13865,9 +14743,15 @@
       <c r="G903" s="3"/>
     </row>
     <row r="904" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A904" s="3"/>
-      <c r="B904" s="3"/>
-      <c r="C904" s="3"/>
+      <c r="A904" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B904" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C904" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D904" s="3">
         <v>4200899</v>
       </c>
@@ -13876,9 +14760,15 @@
       <c r="G904" s="3"/>
     </row>
     <row r="905" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A905" s="3"/>
-      <c r="B905" s="3"/>
-      <c r="C905" s="3"/>
+      <c r="A905" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B905" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D905" s="3">
         <v>4200900</v>
       </c>
@@ -13887,9 +14777,15 @@
       <c r="G905" s="3"/>
     </row>
     <row r="906" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A906" s="3"/>
-      <c r="B906" s="3"/>
-      <c r="C906" s="3"/>
+      <c r="A906" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B906" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D906" s="3">
         <v>4200901</v>
       </c>
@@ -13898,9 +14794,15 @@
       <c r="G906" s="3"/>
     </row>
     <row r="907" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A907" s="3"/>
-      <c r="B907" s="3"/>
-      <c r="C907" s="3"/>
+      <c r="A907" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B907" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D907" s="3">
         <v>4200902</v>
       </c>
@@ -13909,9 +14811,15 @@
       <c r="G907" s="3"/>
     </row>
     <row r="908" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A908" s="3"/>
-      <c r="B908" s="3"/>
-      <c r="C908" s="3"/>
+      <c r="A908" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B908" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D908" s="3">
         <v>4200903</v>
       </c>
@@ -13920,9 +14828,15 @@
       <c r="G908" s="3"/>
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A909" s="3"/>
-      <c r="B909" s="3"/>
-      <c r="C909" s="3"/>
+      <c r="A909" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B909" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D909" s="3">
         <v>4200904</v>
       </c>
@@ -13931,9 +14845,15 @@
       <c r="G909" s="3"/>
     </row>
     <row r="910" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A910" s="3"/>
-      <c r="B910" s="3"/>
-      <c r="C910" s="3"/>
+      <c r="A910" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B910" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D910" s="3">
         <v>4200905</v>
       </c>
@@ -13942,9 +14862,15 @@
       <c r="G910" s="3"/>
     </row>
     <row r="911" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A911" s="3"/>
-      <c r="B911" s="3"/>
-      <c r="C911" s="3"/>
+      <c r="A911" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B911" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D911" s="3">
         <v>4200906</v>
       </c>
@@ -13953,9 +14879,15 @@
       <c r="G911" s="3"/>
     </row>
     <row r="912" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A912" s="3"/>
-      <c r="B912" s="3"/>
-      <c r="C912" s="3"/>
+      <c r="A912" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B912" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D912" s="3">
         <v>4200907</v>
       </c>
@@ -13964,9 +14896,15 @@
       <c r="G912" s="3"/>
     </row>
     <row r="913" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A913" s="3"/>
-      <c r="B913" s="3"/>
-      <c r="C913" s="3"/>
+      <c r="A913" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D913" s="3">
         <v>4200908</v>
       </c>
@@ -13975,9 +14913,15 @@
       <c r="G913" s="3"/>
     </row>
     <row r="914" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A914" s="3"/>
-      <c r="B914" s="3"/>
-      <c r="C914" s="3"/>
+      <c r="A914" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D914" s="3">
         <v>4200909</v>
       </c>
@@ -13986,9 +14930,15 @@
       <c r="G914" s="3"/>
     </row>
     <row r="915" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A915" s="3"/>
-      <c r="B915" s="3"/>
-      <c r="C915" s="3"/>
+      <c r="A915" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D915" s="3">
         <v>4200910</v>
       </c>
@@ -13997,9 +14947,15 @@
       <c r="G915" s="3"/>
     </row>
     <row r="916" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A916" s="3"/>
-      <c r="B916" s="3"/>
-      <c r="C916" s="3"/>
+      <c r="A916" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D916" s="3">
         <v>4200911</v>
       </c>
@@ -14008,9 +14964,15 @@
       <c r="G916" s="3"/>
     </row>
     <row r="917" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A917" s="3"/>
-      <c r="B917" s="3"/>
-      <c r="C917" s="3"/>
+      <c r="A917" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D917" s="3">
         <v>4200912</v>
       </c>
@@ -14019,9 +14981,15 @@
       <c r="G917" s="3"/>
     </row>
     <row r="918" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A918" s="3"/>
-      <c r="B918" s="3"/>
-      <c r="C918" s="3"/>
+      <c r="A918" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B918" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D918" s="3">
         <v>4200913</v>
       </c>
@@ -14030,9 +14998,15 @@
       <c r="G918" s="3"/>
     </row>
     <row r="919" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A919" s="3"/>
-      <c r="B919" s="3"/>
-      <c r="C919" s="3"/>
+      <c r="A919" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B919" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D919" s="3">
         <v>4200914</v>
       </c>
@@ -14041,9 +15015,15 @@
       <c r="G919" s="3"/>
     </row>
     <row r="920" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A920" s="3"/>
-      <c r="B920" s="3"/>
-      <c r="C920" s="3"/>
+      <c r="A920" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C920" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D920" s="3">
         <v>4200915</v>
       </c>
@@ -14052,9 +15032,15 @@
       <c r="G920" s="3"/>
     </row>
     <row r="921" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A921" s="3"/>
-      <c r="B921" s="3"/>
-      <c r="C921" s="3"/>
+      <c r="A921" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B921" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C921" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D921" s="3">
         <v>4200916</v>
       </c>
@@ -14063,9 +15049,15 @@
       <c r="G921" s="3"/>
     </row>
     <row r="922" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A922" s="3"/>
-      <c r="B922" s="3"/>
-      <c r="C922" s="3"/>
+      <c r="A922" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B922" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C922" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D922" s="3">
         <v>4200917</v>
       </c>
@@ -14074,9 +15066,15 @@
       <c r="G922" s="3"/>
     </row>
     <row r="923" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A923" s="3"/>
-      <c r="B923" s="3"/>
-      <c r="C923" s="3"/>
+      <c r="A923" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B923" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C923" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D923" s="3">
         <v>4200918</v>
       </c>
@@ -14085,9 +15083,15 @@
       <c r="G923" s="3"/>
     </row>
     <row r="924" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A924" s="3"/>
-      <c r="B924" s="3"/>
-      <c r="C924" s="3"/>
+      <c r="A924" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B924" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D924" s="3">
         <v>4200919</v>
       </c>
@@ -14096,9 +15100,15 @@
       <c r="G924" s="3"/>
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A925" s="3"/>
-      <c r="B925" s="3"/>
-      <c r="C925" s="3"/>
+      <c r="A925" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B925" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D925" s="3">
         <v>4200920</v>
       </c>
@@ -14107,9 +15117,15 @@
       <c r="G925" s="3"/>
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A926" s="3"/>
-      <c r="B926" s="3"/>
-      <c r="C926" s="3"/>
+      <c r="A926" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B926" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D926" s="3">
         <v>4200921</v>
       </c>
@@ -14118,9 +15134,15 @@
       <c r="G926" s="3"/>
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A927" s="3"/>
-      <c r="B927" s="3"/>
-      <c r="C927" s="3"/>
+      <c r="A927" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D927" s="3">
         <v>4200922</v>
       </c>
@@ -14129,9 +15151,15 @@
       <c r="G927" s="3"/>
     </row>
     <row r="928" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A928" s="3"/>
-      <c r="B928" s="3"/>
-      <c r="C928" s="3"/>
+      <c r="A928" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B928" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D928" s="3">
         <v>4200923</v>
       </c>
@@ -14140,9 +15168,15 @@
       <c r="G928" s="3"/>
     </row>
     <row r="929" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A929" s="3"/>
-      <c r="B929" s="3"/>
-      <c r="C929" s="3"/>
+      <c r="A929" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B929" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D929" s="3">
         <v>4200924</v>
       </c>
@@ -14151,9 +15185,15 @@
       <c r="G929" s="3"/>
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A930" s="3"/>
-      <c r="B930" s="3"/>
-      <c r="C930" s="3"/>
+      <c r="A930" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B930" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D930" s="3">
         <v>4200925</v>
       </c>
@@ -14162,9 +15202,15 @@
       <c r="G930" s="3"/>
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A931" s="3"/>
-      <c r="B931" s="3"/>
-      <c r="C931" s="3"/>
+      <c r="A931" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D931" s="3">
         <v>4200926</v>
       </c>
@@ -14173,9 +15219,15 @@
       <c r="G931" s="3"/>
     </row>
     <row r="932" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A932" s="3"/>
-      <c r="B932" s="3"/>
-      <c r="C932" s="3"/>
+      <c r="A932" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D932" s="3">
         <v>4200927</v>
       </c>
@@ -14184,9 +15236,15 @@
       <c r="G932" s="3"/>
     </row>
     <row r="933" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A933" s="3"/>
-      <c r="B933" s="3"/>
-      <c r="C933" s="3"/>
+      <c r="A933" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B933" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C933" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D933" s="3">
         <v>4200928</v>
       </c>
@@ -14195,9 +15253,15 @@
       <c r="G933" s="3"/>
     </row>
     <row r="934" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A934" s="3"/>
-      <c r="B934" s="3"/>
-      <c r="C934" s="3"/>
+      <c r="A934" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B934" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C934" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D934" s="3">
         <v>4200929</v>
       </c>
@@ -14206,9 +15270,15 @@
       <c r="G934" s="3"/>
     </row>
     <row r="935" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A935" s="3"/>
-      <c r="B935" s="3"/>
-      <c r="C935" s="3"/>
+      <c r="A935" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B935" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C935" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D935" s="3">
         <v>4200930</v>
       </c>
@@ -14217,9 +15287,15 @@
       <c r="G935" s="3"/>
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A936" s="3"/>
-      <c r="B936" s="3"/>
-      <c r="C936" s="3"/>
+      <c r="A936" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B936" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C936" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D936" s="3">
         <v>4200931</v>
       </c>
@@ -14228,9 +15304,15 @@
       <c r="G936" s="3"/>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A937" s="3"/>
-      <c r="B937" s="3"/>
-      <c r="C937" s="3"/>
+      <c r="A937" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B937" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C937" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D937" s="3">
         <v>4200932</v>
       </c>
@@ -15006,8 +16088,12 @@
       <c r="G1006" s="3"/>
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1007" s="3"/>
-      <c r="B1007" s="3"/>
+      <c r="A1007" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1007" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="C1007" s="3" t="s">
         <v>41</v>
       </c>
@@ -15019,8 +16105,12 @@
       <c r="G1007" s="3"/>
     </row>
     <row r="1008" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1008" s="3"/>
-      <c r="B1008" s="3"/>
+      <c r="A1008" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1008" s="3" t="s">
+        <v>419</v>
+      </c>
       <c r="C1008" s="3" t="s">
         <v>41</v>
       </c>
@@ -15032,8 +16122,12 @@
       <c r="G1008" s="3"/>
     </row>
     <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1009" s="3"/>
-      <c r="B1009" s="3"/>
+      <c r="A1009" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1009" s="3" t="s">
+        <v>420</v>
+      </c>
       <c r="C1009" s="3" t="s">
         <v>41</v>
       </c>
@@ -15045,8 +16139,12 @@
       <c r="G1009" s="3"/>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1010" s="3"/>
-      <c r="B1010" s="3"/>
+      <c r="A1010" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1010" s="3" t="s">
+        <v>421</v>
+      </c>
       <c r="C1010" s="3" t="s">
         <v>41</v>
       </c>
@@ -15851,8 +16949,12 @@
       <c r="G1071" s="3"/>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1072" s="3"/>
-      <c r="B1072" s="3"/>
+      <c r="A1072" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>416</v>
+      </c>
       <c r="C1072" s="3" t="s">
         <v>41</v>
       </c>
